--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B473A2-5AA1-4468-B0FF-73B074AE57D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45535079-AECE-4BDB-BF99-610929D9789B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -4146,7 +4146,9 @@
       <c r="F5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="2"/>
+      <c r="G5" s="2">
+        <v>45</v>
+      </c>
       <c r="H5" s="2" t="s">
         <v>77</v>
       </c>
@@ -4202,7 +4204,9 @@
       <c r="F7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="2"/>
+      <c r="G7" s="2">
+        <v>25</v>
+      </c>
       <c r="H7" s="2" t="s">
         <v>77</v>
       </c>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45535079-AECE-4BDB-BF99-610929D9789B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BD1705-C078-4F33-8D51-B10AB1F906C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B5" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Completed")</f>
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B6" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"In Progress")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B8" s="2">
         <f>B4-B5</f>
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B9" s="4">
         <f>IF(B4=0,0,B5/B4)</f>
-        <v>1.7543859649122806E-2</v>
+        <v>4.0935672514619881E-2</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -4144,7 +4144,7 @@
         <v>76</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>5</v>
+        <v>243</v>
       </c>
       <c r="G5" s="2">
         <v>45</v>
@@ -4174,9 +4174,11 @@
         <v>76</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="G6" s="2">
+        <v>30</v>
+      </c>
       <c r="H6" s="2" t="s">
         <v>77</v>
       </c>
@@ -4202,7 +4204,7 @@
         <v>76</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>5</v>
+        <v>243</v>
       </c>
       <c r="G7" s="2">
         <v>25</v>
@@ -4232,9 +4234,11 @@
         <v>76</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="G8" s="2">
+        <v>30</v>
+      </c>
       <c r="H8" s="2" t="s">
         <v>77</v>
       </c>
@@ -8894,15 +8898,15 @@
       </c>
       <c r="D2" s="2">
         <f>COUNTIFS('DSA Problems'!B:B,A2,'DSA Problems'!F:F,"Completed")</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2">
         <f t="shared" ref="E2:E16" si="0">B2-D2</f>
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F2" s="4">
         <f t="shared" ref="F2:F16" si="1">IF(B2=0,0,D2/B2)</f>
-        <v>0.2</v>
+        <v>0.46666666666666667</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -9364,7 +9368,7 @@
       </c>
       <c r="D5" s="2" t="str">
         <f>'DSA Problems'!F5</f>
-        <v>In Progress</v>
+        <v>Completed</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -9389,7 +9393,7 @@
       </c>
       <c r="D6" s="2" t="str">
         <f>'DSA Problems'!F6</f>
-        <v>Not Started</v>
+        <v>Completed</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -9414,7 +9418,7 @@
       </c>
       <c r="D7" s="2" t="str">
         <f>'DSA Problems'!F7</f>
-        <v>In Progress</v>
+        <v>Completed</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -9439,7 +9443,7 @@
       </c>
       <c r="D8" s="2" t="str">
         <f>'DSA Problems'!F8</f>
-        <v>Not Started</v>
+        <v>Completed</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Target-learn\documents\plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Learning\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BD1705-C078-4F33-8D51-B10AB1F906C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18EEE861-EE88-4D19-A8C8-11C0D608138B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B5" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Completed")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B6" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"In Progress")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B8" s="2">
         <f>B4-B5</f>
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B9" s="4">
         <f>IF(B4=0,0,B5/B4)</f>
-        <v>4.0935672514619881E-2</v>
+        <v>4.6783625730994149E-2</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -4264,9 +4264,11 @@
         <v>76</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="G9" s="2">
+        <v>40</v>
+      </c>
       <c r="H9" s="2" t="s">
         <v>77</v>
       </c>
@@ -4292,7 +4294,7 @@
         <v>76</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2" t="s">
@@ -8898,15 +8900,15 @@
       </c>
       <c r="D2" s="2">
         <f>COUNTIFS('DSA Problems'!B:B,A2,'DSA Problems'!F:F,"Completed")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2">
         <f t="shared" ref="E2:E16" si="0">B2-D2</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" s="4">
         <f t="shared" ref="F2:F16" si="1">IF(B2=0,0,D2/B2)</f>
-        <v>0.46666666666666667</v>
+        <v>0.53333333333333333</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -9468,7 +9470,7 @@
       </c>
       <c r="D9" s="2" t="str">
         <f>'DSA Problems'!F9</f>
-        <v>Not Started</v>
+        <v>Completed</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -9493,7 +9495,7 @@
       </c>
       <c r="D10" s="2" t="str">
         <f>'DSA Problems'!F10</f>
-        <v>Not Started</v>
+        <v>In Progress</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Learning\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18EEE861-EE88-4D19-A8C8-11C0D608138B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881198F4-A363-4829-B65A-46D32CB371A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B5" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Completed")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B6" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B8" s="2">
         <f>B4-B5</f>
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="B9" s="4">
         <f>IF(B4=0,0,B5/B4)</f>
-        <v>4.6783625730994149E-2</v>
+        <v>5.2631578947368418E-2</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -4294,9 +4294,11 @@
         <v>76</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="2"/>
+        <v>243</v>
+      </c>
+      <c r="G10" s="2">
+        <v>20</v>
+      </c>
       <c r="H10" s="2" t="s">
         <v>77</v>
       </c>
@@ -8900,15 +8902,15 @@
       </c>
       <c r="D2" s="2">
         <f>COUNTIFS('DSA Problems'!B:B,A2,'DSA Problems'!F:F,"Completed")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2">
         <f t="shared" ref="E2:E16" si="0">B2-D2</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" s="4">
         <f t="shared" ref="F2:F16" si="1">IF(B2=0,0,D2/B2)</f>
-        <v>0.53333333333333333</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -9495,7 +9497,7 @@
       </c>
       <c r="D10" s="2" t="str">
         <f>'DSA Problems'!F10</f>
-        <v>In Progress</v>
+        <v>Completed</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Learning\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{881198F4-A363-4829-B65A-46D32CB371A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6205482-C97F-4338-837F-0344D64B84B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -4492,9 +4492,11 @@
         <v>76</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G17" s="2">
+        <v>20</v>
+      </c>
       <c r="H17" s="2" t="s">
         <v>77</v>
       </c>
@@ -4520,9 +4522,11 @@
         <v>76</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G18" s="2">
+        <v>30</v>
+      </c>
       <c r="H18" s="2" t="s">
         <v>77</v>
       </c>
@@ -9672,7 +9676,7 @@
       </c>
       <c r="D17" s="2" t="str">
         <f>'DSA Problems'!F17</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
@@ -9697,7 +9701,7 @@
       </c>
       <c r="D18" s="2" t="str">
         <f>'DSA Problems'!F18</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Learning\Target-learn\documents\plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6205482-C97F-4338-837F-0344D64B84B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E1BD5D-41CD-45CB-8256-6BD07EE79DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -4552,9 +4552,11 @@
         <v>76</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G19" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G19" s="2">
+        <v>20</v>
+      </c>
       <c r="H19" s="2" t="s">
         <v>77</v>
       </c>
@@ -4580,9 +4582,11 @@
         <v>76</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G20" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G20" s="2">
+        <v>20</v>
+      </c>
       <c r="H20" s="2" t="s">
         <v>77</v>
       </c>
@@ -4608,9 +4612,11 @@
         <v>76</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G21" s="2">
+        <v>25</v>
+      </c>
       <c r="H21" s="2" t="s">
         <v>77</v>
       </c>
@@ -9726,7 +9732,7 @@
       </c>
       <c r="D19" s="2" t="str">
         <f>'DSA Problems'!F19</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
@@ -9751,7 +9757,7 @@
       </c>
       <c r="D20" s="2" t="str">
         <f>'DSA Problems'!F20</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
@@ -9776,7 +9782,7 @@
       </c>
       <c r="D21" s="2" t="str">
         <f>'DSA Problems'!F21</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E1BD5D-41CD-45CB-8256-6BD07EE79DA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2535C60B-613E-4FB5-89D9-49B592A8E13A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1825" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="251">
   <si>
     <t>DSA 90-Day Interview Preparation Dashboard</t>
   </si>
@@ -786,6 +786,12 @@
   </si>
   <si>
     <t>Yes</t>
+  </si>
+  <si>
+    <t>required sliding window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">required more alogorithms </t>
   </si>
 </sst>
 </file>
@@ -1202,7 +1208,7 @@
       </c>
       <c r="B6" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"In Progress")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1211,7 +1217,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -4333,7 +4339,9 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
+      <c r="L11" s="2" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
@@ -4389,7 +4397,9 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
+      <c r="L13" s="2" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
@@ -4417,7 +4427,9 @@
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
+      <c r="L14" s="2" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
@@ -4436,7 +4448,7 @@
         <v>76</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
@@ -4670,7 +4682,7 @@
         <v>76</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2" t="s">
@@ -4698,7 +4710,7 @@
         <v>76</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2" t="s">
@@ -9632,7 +9644,7 @@
       </c>
       <c r="D15" s="2" t="str">
         <f>'DSA Problems'!F15</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
@@ -9832,7 +9844,7 @@
       </c>
       <c r="D23" s="2" t="str">
         <f>'DSA Problems'!F23</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
@@ -9857,7 +9869,7 @@
       </c>
       <c r="D24" s="2" t="str">
         <f>'DSA Problems'!F24</f>
-        <v>Not Started</v>
+        <v>In Progress</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Target-learn\documents\plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Learning\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2535C60B-613E-4FB5-89D9-49B592A8E13A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AADE6069-BEAE-4320-A8BA-9178BDBAA8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -4684,7 +4684,9 @@
       <c r="F23" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G23" s="2"/>
+      <c r="G23" s="2">
+        <v>30</v>
+      </c>
       <c r="H23" s="2" t="s">
         <v>77</v>
       </c>
@@ -5410,9 +5412,11 @@
         <v>76</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G49" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G49" s="2">
+        <v>40</v>
+      </c>
       <c r="H49" s="2" t="s">
         <v>77</v>
       </c>
@@ -5438,9 +5442,11 @@
         <v>76</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G50" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G50" s="2">
+        <v>25</v>
+      </c>
       <c r="H50" s="2" t="s">
         <v>77</v>
       </c>
@@ -10494,7 +10500,7 @@
       </c>
       <c r="D49" s="2" t="str">
         <f>'DSA Problems'!F49</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
@@ -10519,7 +10525,7 @@
       </c>
       <c r="D50" s="2" t="str">
         <f>'DSA Problems'!F50</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Learning\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AADE6069-BEAE-4320-A8BA-9178BDBAA8DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D912C263-723F-4B95-8C5E-7D3E3A872A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1828" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="252">
   <si>
     <t>DSA 90-Day Interview Preparation Dashboard</t>
   </si>
@@ -792,6 +792,9 @@
   </si>
   <si>
     <t xml:space="preserve">required more alogorithms </t>
+  </si>
+  <si>
+    <t>it cannot be executed local</t>
   </si>
 </sst>
 </file>
@@ -1208,7 +1211,7 @@
       </c>
       <c r="B6" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -1217,7 +1220,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -4712,9 +4715,11 @@
         <v>76</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G24" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G24" s="2">
+        <v>20</v>
+      </c>
       <c r="H24" s="2" t="s">
         <v>77</v>
       </c>
@@ -5481,7 +5486,9 @@
       <c r="I51" s="2"/>
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
-      <c r="L51" s="2"/>
+      <c r="L51" s="2" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
@@ -9875,7 +9882,7 @@
       </c>
       <c r="D24" s="2" t="str">
         <f>'DSA Problems'!F24</f>
-        <v>In Progress</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Learning\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D912C263-723F-4B95-8C5E-7D3E3A872A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA8D163-1711-40A2-9FBF-42CB09CE043F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -3993,6 +3993,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:L172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4286,7 +4287,7 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -4316,7 +4317,7 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -4346,7 +4347,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -4434,7 +4435,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -4462,7 +4463,7 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -4520,7 +4521,7 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -4657,9 +4658,11 @@
         <v>76</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G22" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G22" s="2">
+        <v>30</v>
+      </c>
       <c r="H22" s="2" t="s">
         <v>77</v>
       </c>
@@ -4698,7 +4701,7 @@
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -4728,7 +4731,7 @@
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -4756,7 +4759,7 @@
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -4784,7 +4787,7 @@
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -4812,7 +4815,7 @@
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -4896,7 +4899,7 @@
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -4924,7 +4927,7 @@
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -4952,7 +4955,7 @@
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -4980,7 +4983,7 @@
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -5008,7 +5011,7 @@
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -5036,7 +5039,7 @@
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -5064,7 +5067,7 @@
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -5092,7 +5095,7 @@
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -5120,7 +5123,7 @@
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -5148,7 +5151,7 @@
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -5260,7 +5263,7 @@
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -5288,7 +5291,7 @@
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -5344,7 +5347,7 @@
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -5372,7 +5375,7 @@
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -5490,7 +5493,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -5518,7 +5521,7 @@
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -5546,7 +5549,7 @@
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -5574,7 +5577,7 @@
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -5602,7 +5605,7 @@
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -5630,7 +5633,7 @@
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -5658,7 +5661,7 @@
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -5686,7 +5689,7 @@
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -5714,7 +5717,7 @@
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -5770,7 +5773,7 @@
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -5798,7 +5801,7 @@
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -5826,7 +5829,7 @@
       <c r="K63" s="2"/>
       <c r="L63" s="2"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -5882,7 +5885,7 @@
       <c r="K65" s="2"/>
       <c r="L65" s="2"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -5910,7 +5913,7 @@
       <c r="K66" s="2"/>
       <c r="L66" s="2"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -5938,7 +5941,7 @@
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -5966,7 +5969,7 @@
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -5994,7 +5997,7 @@
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -6078,7 +6081,7 @@
       <c r="K72" s="2"/>
       <c r="L72" s="2"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -6106,7 +6109,7 @@
       <c r="K73" s="2"/>
       <c r="L73" s="2"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -6134,7 +6137,7 @@
       <c r="K74" s="2"/>
       <c r="L74" s="2"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -6162,7 +6165,7 @@
       <c r="K75" s="2"/>
       <c r="L75" s="2"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -6302,7 +6305,7 @@
       <c r="K80" s="2"/>
       <c r="L80" s="2"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -6386,7 +6389,7 @@
       <c r="K83" s="2"/>
       <c r="L83" s="2"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -6414,7 +6417,7 @@
       <c r="K84" s="2"/>
       <c r="L84" s="2"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -6442,7 +6445,7 @@
       <c r="K85" s="2"/>
       <c r="L85" s="2"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -6470,7 +6473,7 @@
       <c r="K86" s="2"/>
       <c r="L86" s="2"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -6498,7 +6501,7 @@
       <c r="K87" s="2"/>
       <c r="L87" s="2"/>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -6526,7 +6529,7 @@
       <c r="K88" s="2"/>
       <c r="L88" s="2"/>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -6582,7 +6585,7 @@
       <c r="K90" s="2"/>
       <c r="L90" s="2"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -6610,7 +6613,7 @@
       <c r="K91" s="2"/>
       <c r="L91" s="2"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -6638,7 +6641,7 @@
       <c r="K92" s="2"/>
       <c r="L92" s="2"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -6666,7 +6669,7 @@
       <c r="K93" s="2"/>
       <c r="L93" s="2"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -6694,7 +6697,7 @@
       <c r="K94" s="2"/>
       <c r="L94" s="2"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -6722,7 +6725,7 @@
       <c r="K95" s="2"/>
       <c r="L95" s="2"/>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -6750,7 +6753,7 @@
       <c r="K96" s="2"/>
       <c r="L96" s="2"/>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -6778,7 +6781,7 @@
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -6806,7 +6809,7 @@
       <c r="K98" s="2"/>
       <c r="L98" s="2"/>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -6834,7 +6837,7 @@
       <c r="K99" s="2"/>
       <c r="L99" s="2"/>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -6862,7 +6865,7 @@
       <c r="K100" s="2"/>
       <c r="L100" s="2"/>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -6918,7 +6921,7 @@
       <c r="K102" s="2"/>
       <c r="L102" s="2"/>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -6946,7 +6949,7 @@
       <c r="K103" s="2"/>
       <c r="L103" s="2"/>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -6974,7 +6977,7 @@
       <c r="K104" s="2"/>
       <c r="L104" s="2"/>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>104</v>
       </c>
@@ -7002,7 +7005,7 @@
       <c r="K105" s="2"/>
       <c r="L105" s="2"/>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>105</v>
       </c>
@@ -7198,7 +7201,7 @@
       <c r="K112" s="2"/>
       <c r="L112" s="2"/>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>112</v>
       </c>
@@ -7226,7 +7229,7 @@
       <c r="K113" s="2"/>
       <c r="L113" s="2"/>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>113</v>
       </c>
@@ -7254,7 +7257,7 @@
       <c r="K114" s="2"/>
       <c r="L114" s="2"/>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>114</v>
       </c>
@@ -7338,7 +7341,7 @@
       <c r="K117" s="2"/>
       <c r="L117" s="2"/>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -7394,7 +7397,7 @@
       <c r="K119" s="2"/>
       <c r="L119" s="2"/>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>119</v>
       </c>
@@ -7422,7 +7425,7 @@
       <c r="K120" s="2"/>
       <c r="L120" s="2"/>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>120</v>
       </c>
@@ -7450,7 +7453,7 @@
       <c r="K121" s="2"/>
       <c r="L121" s="2"/>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>121</v>
       </c>
@@ -7478,7 +7481,7 @@
       <c r="K122" s="2"/>
       <c r="L122" s="2"/>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>122</v>
       </c>
@@ -7534,7 +7537,7 @@
       <c r="K124" s="2"/>
       <c r="L124" s="2"/>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>124</v>
       </c>
@@ -7562,7 +7565,7 @@
       <c r="K125" s="2"/>
       <c r="L125" s="2"/>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>125</v>
       </c>
@@ -7590,7 +7593,7 @@
       <c r="K126" s="2"/>
       <c r="L126" s="2"/>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>126</v>
       </c>
@@ -7618,7 +7621,7 @@
       <c r="K127" s="2"/>
       <c r="L127" s="2"/>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>127</v>
       </c>
@@ -7646,7 +7649,7 @@
       <c r="K128" s="2"/>
       <c r="L128" s="2"/>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>128</v>
       </c>
@@ -7674,7 +7677,7 @@
       <c r="K129" s="2"/>
       <c r="L129" s="2"/>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>129</v>
       </c>
@@ -7702,7 +7705,7 @@
       <c r="K130" s="2"/>
       <c r="L130" s="2"/>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>130</v>
       </c>
@@ -7730,7 +7733,7 @@
       <c r="K131" s="2"/>
       <c r="L131" s="2"/>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>131</v>
       </c>
@@ -7758,7 +7761,7 @@
       <c r="K132" s="2"/>
       <c r="L132" s="2"/>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>132</v>
       </c>
@@ -7786,7 +7789,7 @@
       <c r="K133" s="2"/>
       <c r="L133" s="2"/>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>133</v>
       </c>
@@ -7814,7 +7817,7 @@
       <c r="K134" s="2"/>
       <c r="L134" s="2"/>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>134</v>
       </c>
@@ -7842,7 +7845,7 @@
       <c r="K135" s="2"/>
       <c r="L135" s="2"/>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
         <v>135</v>
       </c>
@@ -7898,7 +7901,7 @@
       <c r="K137" s="2"/>
       <c r="L137" s="2"/>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>137</v>
       </c>
@@ -7926,7 +7929,7 @@
       <c r="K138" s="2"/>
       <c r="L138" s="2"/>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
         <v>138</v>
       </c>
@@ -7954,7 +7957,7 @@
       <c r="K139" s="2"/>
       <c r="L139" s="2"/>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
         <v>139</v>
       </c>
@@ -8010,7 +8013,7 @@
       <c r="K141" s="2"/>
       <c r="L141" s="2"/>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
         <v>141</v>
       </c>
@@ -8038,7 +8041,7 @@
       <c r="K142" s="2"/>
       <c r="L142" s="2"/>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
         <v>142</v>
       </c>
@@ -8066,7 +8069,7 @@
       <c r="K143" s="2"/>
       <c r="L143" s="2"/>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
         <v>143</v>
       </c>
@@ -8094,7 +8097,7 @@
       <c r="K144" s="2"/>
       <c r="L144" s="2"/>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
         <v>144</v>
       </c>
@@ -8122,7 +8125,7 @@
       <c r="K145" s="2"/>
       <c r="L145" s="2"/>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>145</v>
       </c>
@@ -8150,7 +8153,7 @@
       <c r="K146" s="2"/>
       <c r="L146" s="2"/>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
         <v>146</v>
       </c>
@@ -8178,7 +8181,7 @@
       <c r="K147" s="2"/>
       <c r="L147" s="2"/>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>147</v>
       </c>
@@ -8206,7 +8209,7 @@
       <c r="K148" s="2"/>
       <c r="L148" s="2"/>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
         <v>148</v>
       </c>
@@ -8234,7 +8237,7 @@
       <c r="K149" s="2"/>
       <c r="L149" s="2"/>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
         <v>149</v>
       </c>
@@ -8262,7 +8265,7 @@
       <c r="K150" s="2"/>
       <c r="L150" s="2"/>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>150</v>
       </c>
@@ -8290,7 +8293,7 @@
       <c r="K151" s="2"/>
       <c r="L151" s="2"/>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>151</v>
       </c>
@@ -8374,7 +8377,7 @@
       <c r="K154" s="2"/>
       <c r="L154" s="2"/>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>154</v>
       </c>
@@ -8402,7 +8405,7 @@
       <c r="K155" s="2"/>
       <c r="L155" s="2"/>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
         <v>155</v>
       </c>
@@ -8430,7 +8433,7 @@
       <c r="K156" s="2"/>
       <c r="L156" s="2"/>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>156</v>
       </c>
@@ -8458,7 +8461,7 @@
       <c r="K157" s="2"/>
       <c r="L157" s="2"/>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
         <v>157</v>
       </c>
@@ -8486,7 +8489,7 @@
       <c r="K158" s="2"/>
       <c r="L158" s="2"/>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>158</v>
       </c>
@@ -8514,7 +8517,7 @@
       <c r="K159" s="2"/>
       <c r="L159" s="2"/>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
         <v>159</v>
       </c>
@@ -8542,7 +8545,7 @@
       <c r="K160" s="2"/>
       <c r="L160" s="2"/>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
         <v>160</v>
       </c>
@@ -8570,7 +8573,7 @@
       <c r="K161" s="2"/>
       <c r="L161" s="2"/>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
         <v>161</v>
       </c>
@@ -8598,7 +8601,7 @@
       <c r="K162" s="2"/>
       <c r="L162" s="2"/>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
         <v>162</v>
       </c>
@@ -8626,7 +8629,7 @@
       <c r="K163" s="2"/>
       <c r="L163" s="2"/>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>163</v>
       </c>
@@ -8654,7 +8657,7 @@
       <c r="K164" s="2"/>
       <c r="L164" s="2"/>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
         <v>164</v>
       </c>
@@ -8682,7 +8685,7 @@
       <c r="K165" s="2"/>
       <c r="L165" s="2"/>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
         <v>165</v>
       </c>
@@ -8710,7 +8713,7 @@
       <c r="K166" s="2"/>
       <c r="L166" s="2"/>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
         <v>166</v>
       </c>
@@ -8738,7 +8741,7 @@
       <c r="K167" s="2"/>
       <c r="L167" s="2"/>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
         <v>167</v>
       </c>
@@ -8766,7 +8769,7 @@
       <c r="K168" s="2"/>
       <c r="L168" s="2"/>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
         <v>168</v>
       </c>
@@ -8794,7 +8797,7 @@
       <c r="K169" s="2"/>
       <c r="L169" s="2"/>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
         <v>169</v>
       </c>
@@ -8822,7 +8825,7 @@
       <c r="K170" s="2"/>
       <c r="L170" s="2"/>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
         <v>170</v>
       </c>
@@ -8850,7 +8853,7 @@
       <c r="K171" s="2"/>
       <c r="L171" s="2"/>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
         <v>171</v>
       </c>
@@ -8879,7 +8882,13 @@
       <c r="L172" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L172" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:L172" xr:uid="{00000000-0009-0000-0000-000002000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Easy"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <dataValidations count="2">
     <dataValidation type="list" sqref="F2:F172" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Not Started,In Progress,Completed,Needs Revision"</formula1>
@@ -9832,7 +9841,7 @@
       </c>
       <c r="D22" s="2" t="str">
         <f>'DSA Problems'!F22</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Learning\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FA8D163-1711-40A2-9FBF-42CB09CE043F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D56808-0C53-4C89-A49E-0972575D24AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4287,7 +4287,7 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -4317,7 +4317,7 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -4347,7 +4347,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -4463,7 +4463,7 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -4491,7 +4491,7 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -4551,7 +4551,7 @@
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -4581,7 +4581,7 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -4611,7 +4611,7 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -4641,7 +4641,7 @@
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -4671,7 +4671,7 @@
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -4843,7 +4843,7 @@
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -4871,7 +4871,7 @@
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -5179,7 +5179,7 @@
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -5207,7 +5207,7 @@
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -5235,7 +5235,7 @@
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -5319,7 +5319,7 @@
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -5403,7 +5403,7 @@
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -5433,7 +5433,7 @@
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -5463,7 +5463,7 @@
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -5745,7 +5745,7 @@
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -5857,7 +5857,7 @@
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -6025,7 +6025,7 @@
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -6053,7 +6053,7 @@
       <c r="K71" s="2"/>
       <c r="L71" s="2"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -6193,7 +6193,7 @@
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -6221,7 +6221,7 @@
       <c r="K77" s="2"/>
       <c r="L77" s="2"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -6249,7 +6249,7 @@
       <c r="K78" s="2"/>
       <c r="L78" s="2"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -6277,7 +6277,7 @@
       <c r="K79" s="2"/>
       <c r="L79" s="2"/>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -6333,7 +6333,7 @@
       <c r="K81" s="2"/>
       <c r="L81" s="2"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -6361,7 +6361,7 @@
       <c r="K82" s="2"/>
       <c r="L82" s="2"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -6557,7 +6557,7 @@
       <c r="K89" s="2"/>
       <c r="L89" s="2"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -6893,7 +6893,7 @@
       <c r="K101" s="2"/>
       <c r="L101" s="2"/>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -7033,7 +7033,7 @@
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>106</v>
       </c>
@@ -7061,7 +7061,7 @@
       <c r="K107" s="2"/>
       <c r="L107" s="2"/>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -7089,7 +7089,7 @@
       <c r="K108" s="2"/>
       <c r="L108" s="2"/>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>108</v>
       </c>
@@ -7117,7 +7117,7 @@
       <c r="K109" s="2"/>
       <c r="L109" s="2"/>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>109</v>
       </c>
@@ -7145,7 +7145,7 @@
       <c r="K110" s="2"/>
       <c r="L110" s="2"/>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>110</v>
       </c>
@@ -7173,7 +7173,7 @@
       <c r="K111" s="2"/>
       <c r="L111" s="2"/>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>111</v>
       </c>
@@ -7285,7 +7285,7 @@
       <c r="K115" s="2"/>
       <c r="L115" s="2"/>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -7313,7 +7313,7 @@
       <c r="K116" s="2"/>
       <c r="L116" s="2"/>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>116</v>
       </c>
@@ -7369,7 +7369,7 @@
       <c r="K118" s="2"/>
       <c r="L118" s="2"/>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>118</v>
       </c>
@@ -7509,7 +7509,7 @@
       <c r="K123" s="2"/>
       <c r="L123" s="2"/>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>123</v>
       </c>
@@ -7873,7 +7873,7 @@
       <c r="K136" s="2"/>
       <c r="L136" s="2"/>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>136</v>
       </c>
@@ -7985,7 +7985,7 @@
       <c r="K140" s="2"/>
       <c r="L140" s="2"/>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>140</v>
       </c>
@@ -8321,7 +8321,7 @@
       <c r="K152" s="2"/>
       <c r="L152" s="2"/>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
         <v>152</v>
       </c>
@@ -8349,7 +8349,7 @@
       <c r="K153" s="2"/>
       <c r="L153" s="2"/>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>153</v>
       </c>
@@ -8883,9 +8883,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L172" xr:uid="{00000000-0009-0000-0000-000002000000}">
-    <filterColumn colId="3">
+    <filterColumn colId="1">
       <filters>
-        <filter val="Easy"/>
+        <filter val="Hashing"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Learning\Target-learn\documents\plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0D56808-0C53-4C89-A49E-0972575D24AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780EBEDD-6AC9-4C5A-B47F-AFBB8E3B7D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -3993,7 +3993,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:L172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4334,9 +4333,11 @@
         <v>76</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G11" s="2">
+        <v>35</v>
+      </c>
       <c r="H11" s="2" t="s">
         <v>77</v>
       </c>
@@ -4491,7 +4492,7 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -4521,7 +4522,7 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -4551,7 +4552,7 @@
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
-    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -4581,7 +4582,7 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
-    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -4611,7 +4612,7 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -4641,7 +4642,7 @@
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
-    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -4671,7 +4672,7 @@
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
-    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -4701,7 +4702,7 @@
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
-    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -4731,7 +4732,7 @@
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -4759,7 +4760,7 @@
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
-    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -4787,7 +4788,7 @@
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -4815,7 +4816,7 @@
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -4843,7 +4844,7 @@
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
     </row>
-    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -4871,7 +4872,7 @@
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
     </row>
-    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -4899,7 +4900,7 @@
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -4927,7 +4928,7 @@
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -4955,7 +4956,7 @@
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -4983,7 +4984,7 @@
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -5011,7 +5012,7 @@
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -5039,7 +5040,7 @@
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -5067,7 +5068,7 @@
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -5095,7 +5096,7 @@
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -5123,7 +5124,7 @@
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -5151,7 +5152,7 @@
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -5179,7 +5180,7 @@
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -5207,7 +5208,7 @@
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -5235,7 +5236,7 @@
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -5263,7 +5264,7 @@
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -5291,7 +5292,7 @@
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
     </row>
-    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -5319,7 +5320,7 @@
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
     </row>
-    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -5347,7 +5348,7 @@
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
     </row>
-    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -5375,7 +5376,7 @@
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
     </row>
-    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -5403,7 +5404,7 @@
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
     </row>
-    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -5433,7 +5434,7 @@
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
     </row>
-    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -5463,7 +5464,7 @@
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
     </row>
-    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -5493,7 +5494,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -5521,7 +5522,7 @@
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
     </row>
-    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -5549,7 +5550,7 @@
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
     </row>
-    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -5577,7 +5578,7 @@
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
     </row>
-    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -5605,7 +5606,7 @@
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
     </row>
-    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -5633,7 +5634,7 @@
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
     </row>
-    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -5661,7 +5662,7 @@
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
     </row>
-    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -5689,7 +5690,7 @@
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
     </row>
-    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -5717,7 +5718,7 @@
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
     </row>
-    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -5745,7 +5746,7 @@
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
     </row>
-    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -5773,7 +5774,7 @@
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
     </row>
-    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -5801,7 +5802,7 @@
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
     </row>
-    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -5829,7 +5830,7 @@
       <c r="K63" s="2"/>
       <c r="L63" s="2"/>
     </row>
-    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -5857,7 +5858,7 @@
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
     </row>
-    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -5885,7 +5886,7 @@
       <c r="K65" s="2"/>
       <c r="L65" s="2"/>
     </row>
-    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -5913,7 +5914,7 @@
       <c r="K66" s="2"/>
       <c r="L66" s="2"/>
     </row>
-    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -5941,7 +5942,7 @@
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
     </row>
-    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -5969,7 +5970,7 @@
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
     </row>
-    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -5997,7 +5998,7 @@
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
     </row>
-    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -6025,7 +6026,7 @@
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
     </row>
-    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -6053,7 +6054,7 @@
       <c r="K71" s="2"/>
       <c r="L71" s="2"/>
     </row>
-    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -6081,7 +6082,7 @@
       <c r="K72" s="2"/>
       <c r="L72" s="2"/>
     </row>
-    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -6109,7 +6110,7 @@
       <c r="K73" s="2"/>
       <c r="L73" s="2"/>
     </row>
-    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -6137,7 +6138,7 @@
       <c r="K74" s="2"/>
       <c r="L74" s="2"/>
     </row>
-    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -6165,7 +6166,7 @@
       <c r="K75" s="2"/>
       <c r="L75" s="2"/>
     </row>
-    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -6193,7 +6194,7 @@
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
     </row>
-    <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -6221,7 +6222,7 @@
       <c r="K77" s="2"/>
       <c r="L77" s="2"/>
     </row>
-    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -6249,7 +6250,7 @@
       <c r="K78" s="2"/>
       <c r="L78" s="2"/>
     </row>
-    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -6277,7 +6278,7 @@
       <c r="K79" s="2"/>
       <c r="L79" s="2"/>
     </row>
-    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -6305,7 +6306,7 @@
       <c r="K80" s="2"/>
       <c r="L80" s="2"/>
     </row>
-    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -6333,7 +6334,7 @@
       <c r="K81" s="2"/>
       <c r="L81" s="2"/>
     </row>
-    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -6361,7 +6362,7 @@
       <c r="K82" s="2"/>
       <c r="L82" s="2"/>
     </row>
-    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -6389,7 +6390,7 @@
       <c r="K83" s="2"/>
       <c r="L83" s="2"/>
     </row>
-    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -6417,7 +6418,7 @@
       <c r="K84" s="2"/>
       <c r="L84" s="2"/>
     </row>
-    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -6445,7 +6446,7 @@
       <c r="K85" s="2"/>
       <c r="L85" s="2"/>
     </row>
-    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -6473,7 +6474,7 @@
       <c r="K86" s="2"/>
       <c r="L86" s="2"/>
     </row>
-    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -6501,7 +6502,7 @@
       <c r="K87" s="2"/>
       <c r="L87" s="2"/>
     </row>
-    <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -6529,7 +6530,7 @@
       <c r="K88" s="2"/>
       <c r="L88" s="2"/>
     </row>
-    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -6557,7 +6558,7 @@
       <c r="K89" s="2"/>
       <c r="L89" s="2"/>
     </row>
-    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -6585,7 +6586,7 @@
       <c r="K90" s="2"/>
       <c r="L90" s="2"/>
     </row>
-    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -6613,7 +6614,7 @@
       <c r="K91" s="2"/>
       <c r="L91" s="2"/>
     </row>
-    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -6641,7 +6642,7 @@
       <c r="K92" s="2"/>
       <c r="L92" s="2"/>
     </row>
-    <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -6669,7 +6670,7 @@
       <c r="K93" s="2"/>
       <c r="L93" s="2"/>
     </row>
-    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -6697,7 +6698,7 @@
       <c r="K94" s="2"/>
       <c r="L94" s="2"/>
     </row>
-    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -6725,7 +6726,7 @@
       <c r="K95" s="2"/>
       <c r="L95" s="2"/>
     </row>
-    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -6753,7 +6754,7 @@
       <c r="K96" s="2"/>
       <c r="L96" s="2"/>
     </row>
-    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -6781,7 +6782,7 @@
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
     </row>
-    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -6809,7 +6810,7 @@
       <c r="K98" s="2"/>
       <c r="L98" s="2"/>
     </row>
-    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -6837,7 +6838,7 @@
       <c r="K99" s="2"/>
       <c r="L99" s="2"/>
     </row>
-    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -6865,7 +6866,7 @@
       <c r="K100" s="2"/>
       <c r="L100" s="2"/>
     </row>
-    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -6893,7 +6894,7 @@
       <c r="K101" s="2"/>
       <c r="L101" s="2"/>
     </row>
-    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -6921,7 +6922,7 @@
       <c r="K102" s="2"/>
       <c r="L102" s="2"/>
     </row>
-    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -6949,7 +6950,7 @@
       <c r="K103" s="2"/>
       <c r="L103" s="2"/>
     </row>
-    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -6977,7 +6978,7 @@
       <c r="K104" s="2"/>
       <c r="L104" s="2"/>
     </row>
-    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>104</v>
       </c>
@@ -7005,7 +7006,7 @@
       <c r="K105" s="2"/>
       <c r="L105" s="2"/>
     </row>
-    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>105</v>
       </c>
@@ -7033,7 +7034,7 @@
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
     </row>
-    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>106</v>
       </c>
@@ -7061,7 +7062,7 @@
       <c r="K107" s="2"/>
       <c r="L107" s="2"/>
     </row>
-    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -7089,7 +7090,7 @@
       <c r="K108" s="2"/>
       <c r="L108" s="2"/>
     </row>
-    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>108</v>
       </c>
@@ -7117,7 +7118,7 @@
       <c r="K109" s="2"/>
       <c r="L109" s="2"/>
     </row>
-    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>109</v>
       </c>
@@ -7145,7 +7146,7 @@
       <c r="K110" s="2"/>
       <c r="L110" s="2"/>
     </row>
-    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>110</v>
       </c>
@@ -7173,7 +7174,7 @@
       <c r="K111" s="2"/>
       <c r="L111" s="2"/>
     </row>
-    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>111</v>
       </c>
@@ -7201,7 +7202,7 @@
       <c r="K112" s="2"/>
       <c r="L112" s="2"/>
     </row>
-    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>112</v>
       </c>
@@ -7229,7 +7230,7 @@
       <c r="K113" s="2"/>
       <c r="L113" s="2"/>
     </row>
-    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>113</v>
       </c>
@@ -7257,7 +7258,7 @@
       <c r="K114" s="2"/>
       <c r="L114" s="2"/>
     </row>
-    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>114</v>
       </c>
@@ -7285,7 +7286,7 @@
       <c r="K115" s="2"/>
       <c r="L115" s="2"/>
     </row>
-    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -7313,7 +7314,7 @@
       <c r="K116" s="2"/>
       <c r="L116" s="2"/>
     </row>
-    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>116</v>
       </c>
@@ -7341,7 +7342,7 @@
       <c r="K117" s="2"/>
       <c r="L117" s="2"/>
     </row>
-    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -7369,7 +7370,7 @@
       <c r="K118" s="2"/>
       <c r="L118" s="2"/>
     </row>
-    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>118</v>
       </c>
@@ -7397,7 +7398,7 @@
       <c r="K119" s="2"/>
       <c r="L119" s="2"/>
     </row>
-    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>119</v>
       </c>
@@ -7425,7 +7426,7 @@
       <c r="K120" s="2"/>
       <c r="L120" s="2"/>
     </row>
-    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>120</v>
       </c>
@@ -7453,7 +7454,7 @@
       <c r="K121" s="2"/>
       <c r="L121" s="2"/>
     </row>
-    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>121</v>
       </c>
@@ -7481,7 +7482,7 @@
       <c r="K122" s="2"/>
       <c r="L122" s="2"/>
     </row>
-    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>122</v>
       </c>
@@ -7509,7 +7510,7 @@
       <c r="K123" s="2"/>
       <c r="L123" s="2"/>
     </row>
-    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>123</v>
       </c>
@@ -7537,7 +7538,7 @@
       <c r="K124" s="2"/>
       <c r="L124" s="2"/>
     </row>
-    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>124</v>
       </c>
@@ -7565,7 +7566,7 @@
       <c r="K125" s="2"/>
       <c r="L125" s="2"/>
     </row>
-    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>125</v>
       </c>
@@ -7593,7 +7594,7 @@
       <c r="K126" s="2"/>
       <c r="L126" s="2"/>
     </row>
-    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>126</v>
       </c>
@@ -7621,7 +7622,7 @@
       <c r="K127" s="2"/>
       <c r="L127" s="2"/>
     </row>
-    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>127</v>
       </c>
@@ -7649,7 +7650,7 @@
       <c r="K128" s="2"/>
       <c r="L128" s="2"/>
     </row>
-    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>128</v>
       </c>
@@ -7677,7 +7678,7 @@
       <c r="K129" s="2"/>
       <c r="L129" s="2"/>
     </row>
-    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>129</v>
       </c>
@@ -7705,7 +7706,7 @@
       <c r="K130" s="2"/>
       <c r="L130" s="2"/>
     </row>
-    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>130</v>
       </c>
@@ -7733,7 +7734,7 @@
       <c r="K131" s="2"/>
       <c r="L131" s="2"/>
     </row>
-    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>131</v>
       </c>
@@ -7761,7 +7762,7 @@
       <c r="K132" s="2"/>
       <c r="L132" s="2"/>
     </row>
-    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>132</v>
       </c>
@@ -7789,7 +7790,7 @@
       <c r="K133" s="2"/>
       <c r="L133" s="2"/>
     </row>
-    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>133</v>
       </c>
@@ -7817,7 +7818,7 @@
       <c r="K134" s="2"/>
       <c r="L134" s="2"/>
     </row>
-    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>134</v>
       </c>
@@ -7845,7 +7846,7 @@
       <c r="K135" s="2"/>
       <c r="L135" s="2"/>
     </row>
-    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
         <v>135</v>
       </c>
@@ -7873,7 +7874,7 @@
       <c r="K136" s="2"/>
       <c r="L136" s="2"/>
     </row>
-    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>136</v>
       </c>
@@ -7901,7 +7902,7 @@
       <c r="K137" s="2"/>
       <c r="L137" s="2"/>
     </row>
-    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>137</v>
       </c>
@@ -7929,7 +7930,7 @@
       <c r="K138" s="2"/>
       <c r="L138" s="2"/>
     </row>
-    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
         <v>138</v>
       </c>
@@ -7957,7 +7958,7 @@
       <c r="K139" s="2"/>
       <c r="L139" s="2"/>
     </row>
-    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
         <v>139</v>
       </c>
@@ -7985,7 +7986,7 @@
       <c r="K140" s="2"/>
       <c r="L140" s="2"/>
     </row>
-    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>140</v>
       </c>
@@ -8013,7 +8014,7 @@
       <c r="K141" s="2"/>
       <c r="L141" s="2"/>
     </row>
-    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
         <v>141</v>
       </c>
@@ -8041,7 +8042,7 @@
       <c r="K142" s="2"/>
       <c r="L142" s="2"/>
     </row>
-    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" s="2">
         <v>142</v>
       </c>
@@ -8069,7 +8070,7 @@
       <c r="K143" s="2"/>
       <c r="L143" s="2"/>
     </row>
-    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" s="2">
         <v>143</v>
       </c>
@@ -8097,7 +8098,7 @@
       <c r="K144" s="2"/>
       <c r="L144" s="2"/>
     </row>
-    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" s="2">
         <v>144</v>
       </c>
@@ -8125,7 +8126,7 @@
       <c r="K145" s="2"/>
       <c r="L145" s="2"/>
     </row>
-    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" s="2">
         <v>145</v>
       </c>
@@ -8153,7 +8154,7 @@
       <c r="K146" s="2"/>
       <c r="L146" s="2"/>
     </row>
-    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" s="2">
         <v>146</v>
       </c>
@@ -8181,7 +8182,7 @@
       <c r="K147" s="2"/>
       <c r="L147" s="2"/>
     </row>
-    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" s="2">
         <v>147</v>
       </c>
@@ -8209,7 +8210,7 @@
       <c r="K148" s="2"/>
       <c r="L148" s="2"/>
     </row>
-    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" s="2">
         <v>148</v>
       </c>
@@ -8237,7 +8238,7 @@
       <c r="K149" s="2"/>
       <c r="L149" s="2"/>
     </row>
-    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" s="2">
         <v>149</v>
       </c>
@@ -8265,7 +8266,7 @@
       <c r="K150" s="2"/>
       <c r="L150" s="2"/>
     </row>
-    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" s="2">
         <v>150</v>
       </c>
@@ -8293,7 +8294,7 @@
       <c r="K151" s="2"/>
       <c r="L151" s="2"/>
     </row>
-    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" s="2">
         <v>151</v>
       </c>
@@ -8321,7 +8322,7 @@
       <c r="K152" s="2"/>
       <c r="L152" s="2"/>
     </row>
-    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" s="2">
         <v>152</v>
       </c>
@@ -8349,7 +8350,7 @@
       <c r="K153" s="2"/>
       <c r="L153" s="2"/>
     </row>
-    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" s="2">
         <v>153</v>
       </c>
@@ -8377,7 +8378,7 @@
       <c r="K154" s="2"/>
       <c r="L154" s="2"/>
     </row>
-    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" s="2">
         <v>154</v>
       </c>
@@ -8405,7 +8406,7 @@
       <c r="K155" s="2"/>
       <c r="L155" s="2"/>
     </row>
-    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" s="2">
         <v>155</v>
       </c>
@@ -8433,7 +8434,7 @@
       <c r="K156" s="2"/>
       <c r="L156" s="2"/>
     </row>
-    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" s="2">
         <v>156</v>
       </c>
@@ -8461,7 +8462,7 @@
       <c r="K157" s="2"/>
       <c r="L157" s="2"/>
     </row>
-    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" s="2">
         <v>157</v>
       </c>
@@ -8489,7 +8490,7 @@
       <c r="K158" s="2"/>
       <c r="L158" s="2"/>
     </row>
-    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" s="2">
         <v>158</v>
       </c>
@@ -8517,7 +8518,7 @@
       <c r="K159" s="2"/>
       <c r="L159" s="2"/>
     </row>
-    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" s="2">
         <v>159</v>
       </c>
@@ -8545,7 +8546,7 @@
       <c r="K160" s="2"/>
       <c r="L160" s="2"/>
     </row>
-    <row r="161" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" s="2">
         <v>160</v>
       </c>
@@ -8573,7 +8574,7 @@
       <c r="K161" s="2"/>
       <c r="L161" s="2"/>
     </row>
-    <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" s="2">
         <v>161</v>
       </c>
@@ -8601,7 +8602,7 @@
       <c r="K162" s="2"/>
       <c r="L162" s="2"/>
     </row>
-    <row r="163" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" s="2">
         <v>162</v>
       </c>
@@ -8629,7 +8630,7 @@
       <c r="K163" s="2"/>
       <c r="L163" s="2"/>
     </row>
-    <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" s="2">
         <v>163</v>
       </c>
@@ -8657,7 +8658,7 @@
       <c r="K164" s="2"/>
       <c r="L164" s="2"/>
     </row>
-    <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" s="2">
         <v>164</v>
       </c>
@@ -8685,7 +8686,7 @@
       <c r="K165" s="2"/>
       <c r="L165" s="2"/>
     </row>
-    <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" s="2">
         <v>165</v>
       </c>
@@ -8713,7 +8714,7 @@
       <c r="K166" s="2"/>
       <c r="L166" s="2"/>
     </row>
-    <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" s="2">
         <v>166</v>
       </c>
@@ -8741,7 +8742,7 @@
       <c r="K167" s="2"/>
       <c r="L167" s="2"/>
     </row>
-    <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" s="2">
         <v>167</v>
       </c>
@@ -8769,7 +8770,7 @@
       <c r="K168" s="2"/>
       <c r="L168" s="2"/>
     </row>
-    <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" s="2">
         <v>168</v>
       </c>
@@ -8797,7 +8798,7 @@
       <c r="K169" s="2"/>
       <c r="L169" s="2"/>
     </row>
-    <row r="170" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" s="2">
         <v>169</v>
       </c>
@@ -8825,7 +8826,7 @@
       <c r="K170" s="2"/>
       <c r="L170" s="2"/>
     </row>
-    <row r="171" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" s="2">
         <v>170</v>
       </c>
@@ -8853,7 +8854,7 @@
       <c r="K171" s="2"/>
       <c r="L171" s="2"/>
     </row>
-    <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" s="2">
         <v>171</v>
       </c>
@@ -8882,13 +8883,7 @@
       <c r="L172" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L172" xr:uid="{00000000-0009-0000-0000-000002000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Hashing"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L172" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="F2:F172" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"Not Started,In Progress,Completed,Needs Revision"</formula1>
@@ -9566,7 +9561,7 @@
       </c>
       <c r="D11" s="2" t="str">
         <f>'DSA Problems'!F11</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780EBEDD-6AC9-4C5A-B47F-AFBB8E3B7D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC3BE49-4286-4E04-A32E-039B9AB6662F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -4365,9 +4365,11 @@
         <v>76</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G12" s="2">
+        <v>40</v>
+      </c>
       <c r="H12" s="2" t="s">
         <v>77</v>
       </c>
@@ -9586,7 +9588,7 @@
       </c>
       <c r="D12" s="2" t="str">
         <f>'DSA Problems'!F12</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Target-learn\documents\plan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDC3BE49-4286-4E04-A32E-039B9AB6662F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F46F43F-AFAD-4017-8772-62300F7B79E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -1163,23 +1163,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="42" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="42" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1205,7 +1205,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -1214,16 +1214,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -1241,11 +1241,11 @@
         <v>5.2631578947368418E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
@@ -1253,7 +1253,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
@@ -1269,11 +1269,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>12</v>
       </c>
@@ -1281,7 +1281,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
@@ -1289,11 +1289,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>16</v>
       </c>
@@ -1301,11 +1301,11 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
@@ -1321,7 +1321,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K91"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="7" customWidth="1"/>
@@ -1335,7 +1335,7 @@
     <col min="11" max="11" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>20</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1399,7 +1399,7 @@
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1428,7 +1428,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1457,7 +1457,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1486,7 +1486,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1515,7 +1515,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1544,7 +1544,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1573,7 +1573,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1602,7 +1602,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1631,7 +1631,7 @@
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1660,7 +1660,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1689,7 +1689,7 @@
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1718,7 +1718,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1747,7 +1747,7 @@
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1776,7 +1776,7 @@
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1805,7 +1805,7 @@
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1834,7 +1834,7 @@
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1863,7 +1863,7 @@
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1892,7 +1892,7 @@
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -1921,7 +1921,7 @@
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1950,7 +1950,7 @@
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1979,7 +1979,7 @@
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -2008,7 +2008,7 @@
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2037,7 +2037,7 @@
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2066,7 +2066,7 @@
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2095,7 +2095,7 @@
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2124,7 +2124,7 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2153,7 +2153,7 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2182,7 +2182,7 @@
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2211,7 +2211,7 @@
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2240,7 +2240,7 @@
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2269,7 +2269,7 @@
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -2298,7 +2298,7 @@
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -2327,7 +2327,7 @@
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2356,7 +2356,7 @@
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -2385,7 +2385,7 @@
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2414,7 +2414,7 @@
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -2443,7 +2443,7 @@
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2472,7 +2472,7 @@
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -2501,7 +2501,7 @@
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -2530,7 +2530,7 @@
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -2559,7 +2559,7 @@
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2588,7 +2588,7 @@
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -2617,7 +2617,7 @@
       <c r="J44" s="2"/>
       <c r="K44" s="2"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -2646,7 +2646,7 @@
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2675,7 +2675,7 @@
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2704,7 +2704,7 @@
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -2733,7 +2733,7 @@
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2762,7 +2762,7 @@
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2791,7 +2791,7 @@
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2820,7 +2820,7 @@
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2849,7 +2849,7 @@
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2878,7 +2878,7 @@
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -2907,7 +2907,7 @@
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -2936,7 +2936,7 @@
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -2965,7 +2965,7 @@
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -2994,7 +2994,7 @@
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -3023,7 +3023,7 @@
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -3052,7 +3052,7 @@
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -3081,7 +3081,7 @@
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -3110,7 +3110,7 @@
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -3139,7 +3139,7 @@
       <c r="J62" s="2"/>
       <c r="K62" s="2"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -3168,7 +3168,7 @@
       <c r="J63" s="2"/>
       <c r="K63" s="2"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -3197,7 +3197,7 @@
       <c r="J64" s="2"/>
       <c r="K64" s="2"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -3226,7 +3226,7 @@
       <c r="J65" s="2"/>
       <c r="K65" s="2"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -3255,7 +3255,7 @@
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -3284,7 +3284,7 @@
       <c r="J67" s="2"/>
       <c r="K67" s="2"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -3313,7 +3313,7 @@
       <c r="J68" s="2"/>
       <c r="K68" s="2"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -3342,7 +3342,7 @@
       <c r="J69" s="2"/>
       <c r="K69" s="2"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -3371,7 +3371,7 @@
       <c r="J70" s="2"/>
       <c r="K70" s="2"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -3400,7 +3400,7 @@
       <c r="J71" s="2"/>
       <c r="K71" s="2"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -3429,7 +3429,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -3458,7 +3458,7 @@
       <c r="J73" s="2"/>
       <c r="K73" s="2"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -3487,7 +3487,7 @@
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -3516,7 +3516,7 @@
       <c r="J75" s="2"/>
       <c r="K75" s="2"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -3545,7 +3545,7 @@
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -3574,7 +3574,7 @@
       <c r="J77" s="2"/>
       <c r="K77" s="2"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -3603,7 +3603,7 @@
       <c r="J78" s="2"/>
       <c r="K78" s="2"/>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -3632,7 +3632,7 @@
       <c r="J79" s="2"/>
       <c r="K79" s="2"/>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -3661,7 +3661,7 @@
       <c r="J80" s="2"/>
       <c r="K80" s="2"/>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -3690,7 +3690,7 @@
       <c r="J81" s="2"/>
       <c r="K81" s="2"/>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -3719,7 +3719,7 @@
       <c r="J82" s="2"/>
       <c r="K82" s="2"/>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -3748,7 +3748,7 @@
       <c r="J83" s="2"/>
       <c r="K83" s="2"/>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -3777,7 +3777,7 @@
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -3806,7 +3806,7 @@
       <c r="J85" s="2"/>
       <c r="K85" s="2"/>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -3835,7 +3835,7 @@
       <c r="J86" s="2"/>
       <c r="K86" s="2"/>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -3864,7 +3864,7 @@
       <c r="J87" s="2"/>
       <c r="K87" s="2"/>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -3893,7 +3893,7 @@
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -3922,7 +3922,7 @@
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -3951,7 +3951,7 @@
       <c r="J90" s="2"/>
       <c r="K90" s="2"/>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -3994,7 +3994,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L172"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -4008,7 +4008,7 @@
     <col min="12" max="12" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>64</v>
       </c>
@@ -4046,7 +4046,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -4076,7 +4076,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -4106,7 +4106,7 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -4136,7 +4136,7 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -4166,7 +4166,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -4196,7 +4196,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -4226,7 +4226,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -4256,7 +4256,7 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -4286,7 +4286,7 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -4316,7 +4316,7 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -4378,7 +4378,7 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -4395,9 +4395,11 @@
         <v>76</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G13" s="2">
+        <v>30</v>
+      </c>
       <c r="H13" s="2" t="s">
         <v>77</v>
       </c>
@@ -4408,7 +4410,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -4438,7 +4440,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -4457,7 +4459,9 @@
       <c r="F15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G15" s="2"/>
+      <c r="G15" s="2">
+        <v>25</v>
+      </c>
       <c r="H15" s="2" t="s">
         <v>77</v>
       </c>
@@ -4466,7 +4470,7 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -4494,7 +4498,7 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -4524,7 +4528,7 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -4554,7 +4558,7 @@
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -4584,7 +4588,7 @@
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -4614,7 +4618,7 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -4644,7 +4648,7 @@
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -4674,7 +4678,7 @@
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -4704,7 +4708,7 @@
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -4734,7 +4738,7 @@
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -4762,7 +4766,7 @@
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -4790,7 +4794,7 @@
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -4818,7 +4822,7 @@
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -4846,7 +4850,7 @@
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -4874,7 +4878,7 @@
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -4902,7 +4906,7 @@
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -4930,7 +4934,7 @@
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -4958,7 +4962,7 @@
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -4986,7 +4990,7 @@
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -5014,7 +5018,7 @@
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -5042,7 +5046,7 @@
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -5070,7 +5074,7 @@
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -5098,7 +5102,7 @@
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -5126,7 +5130,7 @@
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -5154,7 +5158,7 @@
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -5182,7 +5186,7 @@
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -5210,7 +5214,7 @@
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -5238,7 +5242,7 @@
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -5266,7 +5270,7 @@
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -5294,7 +5298,7 @@
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -5322,7 +5326,7 @@
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -5350,7 +5354,7 @@
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -5378,7 +5382,7 @@
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -5406,7 +5410,7 @@
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -5436,7 +5440,7 @@
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -5466,7 +5470,7 @@
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -5496,7 +5500,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -5524,7 +5528,7 @@
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -5552,7 +5556,7 @@
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -5580,7 +5584,7 @@
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -5608,7 +5612,7 @@
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -5636,7 +5640,7 @@
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -5664,7 +5668,7 @@
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -5692,7 +5696,7 @@
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -5720,7 +5724,7 @@
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -5748,7 +5752,7 @@
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -5776,7 +5780,7 @@
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -5804,7 +5808,7 @@
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -5832,7 +5836,7 @@
       <c r="K63" s="2"/>
       <c r="L63" s="2"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -5860,7 +5864,7 @@
       <c r="K64" s="2"/>
       <c r="L64" s="2"/>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -5888,7 +5892,7 @@
       <c r="K65" s="2"/>
       <c r="L65" s="2"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -5916,7 +5920,7 @@
       <c r="K66" s="2"/>
       <c r="L66" s="2"/>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -5944,7 +5948,7 @@
       <c r="K67" s="2"/>
       <c r="L67" s="2"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -5972,7 +5976,7 @@
       <c r="K68" s="2"/>
       <c r="L68" s="2"/>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -6000,7 +6004,7 @@
       <c r="K69" s="2"/>
       <c r="L69" s="2"/>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -6028,7 +6032,7 @@
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -6056,7 +6060,7 @@
       <c r="K71" s="2"/>
       <c r="L71" s="2"/>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -6084,7 +6088,7 @@
       <c r="K72" s="2"/>
       <c r="L72" s="2"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -6112,7 +6116,7 @@
       <c r="K73" s="2"/>
       <c r="L73" s="2"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -6140,7 +6144,7 @@
       <c r="K74" s="2"/>
       <c r="L74" s="2"/>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -6168,7 +6172,7 @@
       <c r="K75" s="2"/>
       <c r="L75" s="2"/>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -6196,7 +6200,7 @@
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -6224,7 +6228,7 @@
       <c r="K77" s="2"/>
       <c r="L77" s="2"/>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -6252,7 +6256,7 @@
       <c r="K78" s="2"/>
       <c r="L78" s="2"/>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -6280,7 +6284,7 @@
       <c r="K79" s="2"/>
       <c r="L79" s="2"/>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -6308,7 +6312,7 @@
       <c r="K80" s="2"/>
       <c r="L80" s="2"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -6336,7 +6340,7 @@
       <c r="K81" s="2"/>
       <c r="L81" s="2"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -6364,7 +6368,7 @@
       <c r="K82" s="2"/>
       <c r="L82" s="2"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -6392,7 +6396,7 @@
       <c r="K83" s="2"/>
       <c r="L83" s="2"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -6420,7 +6424,7 @@
       <c r="K84" s="2"/>
       <c r="L84" s="2"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -6448,7 +6452,7 @@
       <c r="K85" s="2"/>
       <c r="L85" s="2"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -6476,7 +6480,7 @@
       <c r="K86" s="2"/>
       <c r="L86" s="2"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -6504,7 +6508,7 @@
       <c r="K87" s="2"/>
       <c r="L87" s="2"/>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -6532,7 +6536,7 @@
       <c r="K88" s="2"/>
       <c r="L88" s="2"/>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -6560,7 +6564,7 @@
       <c r="K89" s="2"/>
       <c r="L89" s="2"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -6588,7 +6592,7 @@
       <c r="K90" s="2"/>
       <c r="L90" s="2"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -6616,7 +6620,7 @@
       <c r="K91" s="2"/>
       <c r="L91" s="2"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -6644,7 +6648,7 @@
       <c r="K92" s="2"/>
       <c r="L92" s="2"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -6672,7 +6676,7 @@
       <c r="K93" s="2"/>
       <c r="L93" s="2"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -6700,7 +6704,7 @@
       <c r="K94" s="2"/>
       <c r="L94" s="2"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -6728,7 +6732,7 @@
       <c r="K95" s="2"/>
       <c r="L95" s="2"/>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -6756,7 +6760,7 @@
       <c r="K96" s="2"/>
       <c r="L96" s="2"/>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -6784,7 +6788,7 @@
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -6812,7 +6816,7 @@
       <c r="K98" s="2"/>
       <c r="L98" s="2"/>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -6840,7 +6844,7 @@
       <c r="K99" s="2"/>
       <c r="L99" s="2"/>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -6868,7 +6872,7 @@
       <c r="K100" s="2"/>
       <c r="L100" s="2"/>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -6896,7 +6900,7 @@
       <c r="K101" s="2"/>
       <c r="L101" s="2"/>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -6924,7 +6928,7 @@
       <c r="K102" s="2"/>
       <c r="L102" s="2"/>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -6952,7 +6956,7 @@
       <c r="K103" s="2"/>
       <c r="L103" s="2"/>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -6980,7 +6984,7 @@
       <c r="K104" s="2"/>
       <c r="L104" s="2"/>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>104</v>
       </c>
@@ -7008,7 +7012,7 @@
       <c r="K105" s="2"/>
       <c r="L105" s="2"/>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>105</v>
       </c>
@@ -7036,7 +7040,7 @@
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>106</v>
       </c>
@@ -7064,7 +7068,7 @@
       <c r="K107" s="2"/>
       <c r="L107" s="2"/>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -7092,7 +7096,7 @@
       <c r="K108" s="2"/>
       <c r="L108" s="2"/>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>108</v>
       </c>
@@ -7120,7 +7124,7 @@
       <c r="K109" s="2"/>
       <c r="L109" s="2"/>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>109</v>
       </c>
@@ -7148,7 +7152,7 @@
       <c r="K110" s="2"/>
       <c r="L110" s="2"/>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>110</v>
       </c>
@@ -7176,7 +7180,7 @@
       <c r="K111" s="2"/>
       <c r="L111" s="2"/>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>111</v>
       </c>
@@ -7204,7 +7208,7 @@
       <c r="K112" s="2"/>
       <c r="L112" s="2"/>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>112</v>
       </c>
@@ -7232,7 +7236,7 @@
       <c r="K113" s="2"/>
       <c r="L113" s="2"/>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>113</v>
       </c>
@@ -7260,7 +7264,7 @@
       <c r="K114" s="2"/>
       <c r="L114" s="2"/>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>114</v>
       </c>
@@ -7288,7 +7292,7 @@
       <c r="K115" s="2"/>
       <c r="L115" s="2"/>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -7316,7 +7320,7 @@
       <c r="K116" s="2"/>
       <c r="L116" s="2"/>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>116</v>
       </c>
@@ -7344,7 +7348,7 @@
       <c r="K117" s="2"/>
       <c r="L117" s="2"/>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -7372,7 +7376,7 @@
       <c r="K118" s="2"/>
       <c r="L118" s="2"/>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>118</v>
       </c>
@@ -7400,7 +7404,7 @@
       <c r="K119" s="2"/>
       <c r="L119" s="2"/>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>119</v>
       </c>
@@ -7428,7 +7432,7 @@
       <c r="K120" s="2"/>
       <c r="L120" s="2"/>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>120</v>
       </c>
@@ -7456,7 +7460,7 @@
       <c r="K121" s="2"/>
       <c r="L121" s="2"/>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>121</v>
       </c>
@@ -7484,7 +7488,7 @@
       <c r="K122" s="2"/>
       <c r="L122" s="2"/>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>122</v>
       </c>
@@ -7512,7 +7516,7 @@
       <c r="K123" s="2"/>
       <c r="L123" s="2"/>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>123</v>
       </c>
@@ -7540,7 +7544,7 @@
       <c r="K124" s="2"/>
       <c r="L124" s="2"/>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>124</v>
       </c>
@@ -7568,7 +7572,7 @@
       <c r="K125" s="2"/>
       <c r="L125" s="2"/>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>125</v>
       </c>
@@ -7596,7 +7600,7 @@
       <c r="K126" s="2"/>
       <c r="L126" s="2"/>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>126</v>
       </c>
@@ -7624,7 +7628,7 @@
       <c r="K127" s="2"/>
       <c r="L127" s="2"/>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>127</v>
       </c>
@@ -7652,7 +7656,7 @@
       <c r="K128" s="2"/>
       <c r="L128" s="2"/>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>128</v>
       </c>
@@ -7680,7 +7684,7 @@
       <c r="K129" s="2"/>
       <c r="L129" s="2"/>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>129</v>
       </c>
@@ -7708,7 +7712,7 @@
       <c r="K130" s="2"/>
       <c r="L130" s="2"/>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>130</v>
       </c>
@@ -7736,7 +7740,7 @@
       <c r="K131" s="2"/>
       <c r="L131" s="2"/>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>131</v>
       </c>
@@ -7764,7 +7768,7 @@
       <c r="K132" s="2"/>
       <c r="L132" s="2"/>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>132</v>
       </c>
@@ -7792,7 +7796,7 @@
       <c r="K133" s="2"/>
       <c r="L133" s="2"/>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>133</v>
       </c>
@@ -7820,7 +7824,7 @@
       <c r="K134" s="2"/>
       <c r="L134" s="2"/>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <v>134</v>
       </c>
@@ -7848,7 +7852,7 @@
       <c r="K135" s="2"/>
       <c r="L135" s="2"/>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>135</v>
       </c>
@@ -7876,7 +7880,7 @@
       <c r="K136" s="2"/>
       <c r="L136" s="2"/>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <v>136</v>
       </c>
@@ -7904,7 +7908,7 @@
       <c r="K137" s="2"/>
       <c r="L137" s="2"/>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>137</v>
       </c>
@@ -7932,7 +7936,7 @@
       <c r="K138" s="2"/>
       <c r="L138" s="2"/>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
         <v>138</v>
       </c>
@@ -7960,7 +7964,7 @@
       <c r="K139" s="2"/>
       <c r="L139" s="2"/>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <v>139</v>
       </c>
@@ -7988,7 +7992,7 @@
       <c r="K140" s="2"/>
       <c r="L140" s="2"/>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A141" s="2">
         <v>140</v>
       </c>
@@ -8016,7 +8020,7 @@
       <c r="K141" s="2"/>
       <c r="L141" s="2"/>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <v>141</v>
       </c>
@@ -8044,7 +8048,7 @@
       <c r="K142" s="2"/>
       <c r="L142" s="2"/>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A143" s="2">
         <v>142</v>
       </c>
@@ -8072,7 +8076,7 @@
       <c r="K143" s="2"/>
       <c r="L143" s="2"/>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A144" s="2">
         <v>143</v>
       </c>
@@ -8100,7 +8104,7 @@
       <c r="K144" s="2"/>
       <c r="L144" s="2"/>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A145" s="2">
         <v>144</v>
       </c>
@@ -8128,7 +8132,7 @@
       <c r="K145" s="2"/>
       <c r="L145" s="2"/>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A146" s="2">
         <v>145</v>
       </c>
@@ -8156,7 +8160,7 @@
       <c r="K146" s="2"/>
       <c r="L146" s="2"/>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A147" s="2">
         <v>146</v>
       </c>
@@ -8184,7 +8188,7 @@
       <c r="K147" s="2"/>
       <c r="L147" s="2"/>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A148" s="2">
         <v>147</v>
       </c>
@@ -8212,7 +8216,7 @@
       <c r="K148" s="2"/>
       <c r="L148" s="2"/>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A149" s="2">
         <v>148</v>
       </c>
@@ -8240,7 +8244,7 @@
       <c r="K149" s="2"/>
       <c r="L149" s="2"/>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A150" s="2">
         <v>149</v>
       </c>
@@ -8268,7 +8272,7 @@
       <c r="K150" s="2"/>
       <c r="L150" s="2"/>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A151" s="2">
         <v>150</v>
       </c>
@@ -8296,7 +8300,7 @@
       <c r="K151" s="2"/>
       <c r="L151" s="2"/>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A152" s="2">
         <v>151</v>
       </c>
@@ -8324,7 +8328,7 @@
       <c r="K152" s="2"/>
       <c r="L152" s="2"/>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A153" s="2">
         <v>152</v>
       </c>
@@ -8352,7 +8356,7 @@
       <c r="K153" s="2"/>
       <c r="L153" s="2"/>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A154" s="2">
         <v>153</v>
       </c>
@@ -8380,7 +8384,7 @@
       <c r="K154" s="2"/>
       <c r="L154" s="2"/>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A155" s="2">
         <v>154</v>
       </c>
@@ -8408,7 +8412,7 @@
       <c r="K155" s="2"/>
       <c r="L155" s="2"/>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A156" s="2">
         <v>155</v>
       </c>
@@ -8436,7 +8440,7 @@
       <c r="K156" s="2"/>
       <c r="L156" s="2"/>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A157" s="2">
         <v>156</v>
       </c>
@@ -8464,7 +8468,7 @@
       <c r="K157" s="2"/>
       <c r="L157" s="2"/>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A158" s="2">
         <v>157</v>
       </c>
@@ -8492,7 +8496,7 @@
       <c r="K158" s="2"/>
       <c r="L158" s="2"/>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A159" s="2">
         <v>158</v>
       </c>
@@ -8520,7 +8524,7 @@
       <c r="K159" s="2"/>
       <c r="L159" s="2"/>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A160" s="2">
         <v>159</v>
       </c>
@@ -8548,7 +8552,7 @@
       <c r="K160" s="2"/>
       <c r="L160" s="2"/>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A161" s="2">
         <v>160</v>
       </c>
@@ -8576,7 +8580,7 @@
       <c r="K161" s="2"/>
       <c r="L161" s="2"/>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A162" s="2">
         <v>161</v>
       </c>
@@ -8604,7 +8608,7 @@
       <c r="K162" s="2"/>
       <c r="L162" s="2"/>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A163" s="2">
         <v>162</v>
       </c>
@@ -8632,7 +8636,7 @@
       <c r="K163" s="2"/>
       <c r="L163" s="2"/>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A164" s="2">
         <v>163</v>
       </c>
@@ -8660,7 +8664,7 @@
       <c r="K164" s="2"/>
       <c r="L164" s="2"/>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A165" s="2">
         <v>164</v>
       </c>
@@ -8688,7 +8692,7 @@
       <c r="K165" s="2"/>
       <c r="L165" s="2"/>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A166" s="2">
         <v>165</v>
       </c>
@@ -8716,7 +8720,7 @@
       <c r="K166" s="2"/>
       <c r="L166" s="2"/>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A167" s="2">
         <v>166</v>
       </c>
@@ -8744,7 +8748,7 @@
       <c r="K167" s="2"/>
       <c r="L167" s="2"/>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A168" s="2">
         <v>167</v>
       </c>
@@ -8772,7 +8776,7 @@
       <c r="K168" s="2"/>
       <c r="L168" s="2"/>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A169" s="2">
         <v>168</v>
       </c>
@@ -8800,7 +8804,7 @@
       <c r="K169" s="2"/>
       <c r="L169" s="2"/>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A170" s="2">
         <v>169</v>
       </c>
@@ -8828,7 +8832,7 @@
       <c r="K170" s="2"/>
       <c r="L170" s="2"/>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A171" s="2">
         <v>170</v>
       </c>
@@ -8856,7 +8860,7 @@
       <c r="K171" s="2"/>
       <c r="L171" s="2"/>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A172" s="2">
         <v>171</v>
       </c>
@@ -8901,7 +8905,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -8911,7 +8915,7 @@
     <col min="6" max="6" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>65</v>
       </c>
@@ -8931,7 +8935,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>32</v>
       </c>
@@ -8954,7 +8958,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>38</v>
       </c>
@@ -8977,7 +8981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>42</v>
       </c>
@@ -9000,7 +9004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>41</v>
       </c>
@@ -9023,7 +9027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>43</v>
       </c>
@@ -9046,7 +9050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>46</v>
       </c>
@@ -9069,7 +9073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>47</v>
       </c>
@@ -9092,7 +9096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>48</v>
       </c>
@@ -9115,7 +9119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>164</v>
       </c>
@@ -9138,7 +9142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>50</v>
       </c>
@@ -9161,7 +9165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>51</v>
       </c>
@@ -9184,7 +9188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>52</v>
       </c>
@@ -9207,7 +9211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>54</v>
       </c>
@@ -9230,7 +9234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>55</v>
       </c>
@@ -9253,7 +9257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>56</v>
       </c>
@@ -9284,7 +9288,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I172"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="50" customWidth="1"/>
@@ -9294,7 +9298,7 @@
     <col min="9" max="9" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>244</v>
       </c>
@@ -9323,7 +9327,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <f>'DSA Problems'!A2</f>
         <v>1</v>
@@ -9348,7 +9352,7 @@
       </c>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <f>'DSA Problems'!A3</f>
         <v>2</v>
@@ -9373,7 +9377,7 @@
       </c>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <f>'DSA Problems'!A4</f>
         <v>3</v>
@@ -9398,7 +9402,7 @@
       </c>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <f>'DSA Problems'!A5</f>
         <v>4</v>
@@ -9423,7 +9427,7 @@
       </c>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <f>'DSA Problems'!A6</f>
         <v>5</v>
@@ -9448,7 +9452,7 @@
       </c>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <f>'DSA Problems'!A7</f>
         <v>6</v>
@@ -9473,7 +9477,7 @@
       </c>
       <c r="I7" s="2"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <f>'DSA Problems'!A8</f>
         <v>7</v>
@@ -9498,7 +9502,7 @@
       </c>
       <c r="I8" s="2"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <f>'DSA Problems'!A9</f>
         <v>8</v>
@@ -9523,7 +9527,7 @@
       </c>
       <c r="I9" s="2"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <f>'DSA Problems'!A10</f>
         <v>9</v>
@@ -9548,7 +9552,7 @@
       </c>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <f>'DSA Problems'!A11</f>
         <v>10</v>
@@ -9573,7 +9577,7 @@
       </c>
       <c r="I11" s="2"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <f>'DSA Problems'!A12</f>
         <v>11</v>
@@ -9598,7 +9602,7 @@
       </c>
       <c r="I12" s="2"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <f>'DSA Problems'!A13</f>
         <v>12</v>
@@ -9613,7 +9617,7 @@
       </c>
       <c r="D13" s="2" t="str">
         <f>'DSA Problems'!F13</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
@@ -9623,7 +9627,7 @@
       </c>
       <c r="I13" s="2"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <f>'DSA Problems'!A14</f>
         <v>13</v>
@@ -9648,7 +9652,7 @@
       </c>
       <c r="I14" s="2"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <f>'DSA Problems'!A15</f>
         <v>14</v>
@@ -9673,7 +9677,7 @@
       </c>
       <c r="I15" s="2"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <f>'DSA Problems'!A16</f>
         <v>15</v>
@@ -9698,7 +9702,7 @@
       </c>
       <c r="I16" s="2"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <f>'DSA Problems'!A17</f>
         <v>16</v>
@@ -9723,7 +9727,7 @@
       </c>
       <c r="I17" s="2"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <f>'DSA Problems'!A18</f>
         <v>17</v>
@@ -9748,7 +9752,7 @@
       </c>
       <c r="I18" s="2"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <f>'DSA Problems'!A19</f>
         <v>18</v>
@@ -9773,7 +9777,7 @@
       </c>
       <c r="I19" s="2"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <f>'DSA Problems'!A20</f>
         <v>19</v>
@@ -9798,7 +9802,7 @@
       </c>
       <c r="I20" s="2"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <f>'DSA Problems'!A21</f>
         <v>20</v>
@@ -9823,7 +9827,7 @@
       </c>
       <c r="I21" s="2"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <f>'DSA Problems'!A22</f>
         <v>21</v>
@@ -9848,7 +9852,7 @@
       </c>
       <c r="I22" s="2"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <f>'DSA Problems'!A23</f>
         <v>22</v>
@@ -9873,7 +9877,7 @@
       </c>
       <c r="I23" s="2"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <f>'DSA Problems'!A24</f>
         <v>23</v>
@@ -9898,7 +9902,7 @@
       </c>
       <c r="I24" s="2"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <f>'DSA Problems'!A25</f>
         <v>24</v>
@@ -9923,7 +9927,7 @@
       </c>
       <c r="I25" s="2"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <f>'DSA Problems'!A26</f>
         <v>25</v>
@@ -9948,7 +9952,7 @@
       </c>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <f>'DSA Problems'!A27</f>
         <v>26</v>
@@ -9973,7 +9977,7 @@
       </c>
       <c r="I27" s="2"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <f>'DSA Problems'!A28</f>
         <v>27</v>
@@ -9998,7 +10002,7 @@
       </c>
       <c r="I28" s="2"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <f>'DSA Problems'!A29</f>
         <v>28</v>
@@ -10023,7 +10027,7 @@
       </c>
       <c r="I29" s="2"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <f>'DSA Problems'!A30</f>
         <v>29</v>
@@ -10048,7 +10052,7 @@
       </c>
       <c r="I30" s="2"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <f>'DSA Problems'!A31</f>
         <v>30</v>
@@ -10073,7 +10077,7 @@
       </c>
       <c r="I31" s="2"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <f>'DSA Problems'!A32</f>
         <v>31</v>
@@ -10098,7 +10102,7 @@
       </c>
       <c r="I32" s="2"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <f>'DSA Problems'!A33</f>
         <v>32</v>
@@ -10123,7 +10127,7 @@
       </c>
       <c r="I33" s="2"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <f>'DSA Problems'!A34</f>
         <v>33</v>
@@ -10148,7 +10152,7 @@
       </c>
       <c r="I34" s="2"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <f>'DSA Problems'!A35</f>
         <v>34</v>
@@ -10173,7 +10177,7 @@
       </c>
       <c r="I35" s="2"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <f>'DSA Problems'!A36</f>
         <v>35</v>
@@ -10198,7 +10202,7 @@
       </c>
       <c r="I36" s="2"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <f>'DSA Problems'!A37</f>
         <v>36</v>
@@ -10223,7 +10227,7 @@
       </c>
       <c r="I37" s="2"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <f>'DSA Problems'!A38</f>
         <v>37</v>
@@ -10248,7 +10252,7 @@
       </c>
       <c r="I38" s="2"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <f>'DSA Problems'!A39</f>
         <v>38</v>
@@ -10273,7 +10277,7 @@
       </c>
       <c r="I39" s="2"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <f>'DSA Problems'!A40</f>
         <v>39</v>
@@ -10298,7 +10302,7 @@
       </c>
       <c r="I40" s="2"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <f>'DSA Problems'!A41</f>
         <v>40</v>
@@ -10323,7 +10327,7 @@
       </c>
       <c r="I41" s="2"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <f>'DSA Problems'!A42</f>
         <v>41</v>
@@ -10348,7 +10352,7 @@
       </c>
       <c r="I42" s="2"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <f>'DSA Problems'!A43</f>
         <v>42</v>
@@ -10373,7 +10377,7 @@
       </c>
       <c r="I43" s="2"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <f>'DSA Problems'!A44</f>
         <v>43</v>
@@ -10398,7 +10402,7 @@
       </c>
       <c r="I44" s="2"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <f>'DSA Problems'!A45</f>
         <v>44</v>
@@ -10423,7 +10427,7 @@
       </c>
       <c r="I45" s="2"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <f>'DSA Problems'!A46</f>
         <v>45</v>
@@ -10448,7 +10452,7 @@
       </c>
       <c r="I46" s="2"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <f>'DSA Problems'!A47</f>
         <v>46</v>
@@ -10473,7 +10477,7 @@
       </c>
       <c r="I47" s="2"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <f>'DSA Problems'!A48</f>
         <v>47</v>
@@ -10498,7 +10502,7 @@
       </c>
       <c r="I48" s="2"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <f>'DSA Problems'!A49</f>
         <v>48</v>
@@ -10523,7 +10527,7 @@
       </c>
       <c r="I49" s="2"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <f>'DSA Problems'!A50</f>
         <v>49</v>
@@ -10548,7 +10552,7 @@
       </c>
       <c r="I50" s="2"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <f>'DSA Problems'!A51</f>
         <v>50</v>
@@ -10573,7 +10577,7 @@
       </c>
       <c r="I51" s="2"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <f>'DSA Problems'!A52</f>
         <v>51</v>
@@ -10598,7 +10602,7 @@
       </c>
       <c r="I52" s="2"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <f>'DSA Problems'!A53</f>
         <v>52</v>
@@ -10623,7 +10627,7 @@
       </c>
       <c r="I53" s="2"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <f>'DSA Problems'!A54</f>
         <v>53</v>
@@ -10648,7 +10652,7 @@
       </c>
       <c r="I54" s="2"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <f>'DSA Problems'!A55</f>
         <v>54</v>
@@ -10673,7 +10677,7 @@
       </c>
       <c r="I55" s="2"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <f>'DSA Problems'!A56</f>
         <v>55</v>
@@ -10698,7 +10702,7 @@
       </c>
       <c r="I56" s="2"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <f>'DSA Problems'!A57</f>
         <v>56</v>
@@ -10723,7 +10727,7 @@
       </c>
       <c r="I57" s="2"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <f>'DSA Problems'!A58</f>
         <v>57</v>
@@ -10748,7 +10752,7 @@
       </c>
       <c r="I58" s="2"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <f>'DSA Problems'!A59</f>
         <v>58</v>
@@ -10773,7 +10777,7 @@
       </c>
       <c r="I59" s="2"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <f>'DSA Problems'!A60</f>
         <v>59</v>
@@ -10798,7 +10802,7 @@
       </c>
       <c r="I60" s="2"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <f>'DSA Problems'!A61</f>
         <v>60</v>
@@ -10823,7 +10827,7 @@
       </c>
       <c r="I61" s="2"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <f>'DSA Problems'!A62</f>
         <v>61</v>
@@ -10848,7 +10852,7 @@
       </c>
       <c r="I62" s="2"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <f>'DSA Problems'!A63</f>
         <v>62</v>
@@ -10873,7 +10877,7 @@
       </c>
       <c r="I63" s="2"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <f>'DSA Problems'!A64</f>
         <v>63</v>
@@ -10898,7 +10902,7 @@
       </c>
       <c r="I64" s="2"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <f>'DSA Problems'!A65</f>
         <v>64</v>
@@ -10923,7 +10927,7 @@
       </c>
       <c r="I65" s="2"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <f>'DSA Problems'!A66</f>
         <v>65</v>
@@ -10948,7 +10952,7 @@
       </c>
       <c r="I66" s="2"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <f>'DSA Problems'!A67</f>
         <v>66</v>
@@ -10973,7 +10977,7 @@
       </c>
       <c r="I67" s="2"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <f>'DSA Problems'!A68</f>
         <v>67</v>
@@ -10998,7 +11002,7 @@
       </c>
       <c r="I68" s="2"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <f>'DSA Problems'!A69</f>
         <v>68</v>
@@ -11023,7 +11027,7 @@
       </c>
       <c r="I69" s="2"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <f>'DSA Problems'!A70</f>
         <v>69</v>
@@ -11048,7 +11052,7 @@
       </c>
       <c r="I70" s="2"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <f>'DSA Problems'!A71</f>
         <v>70</v>
@@ -11073,7 +11077,7 @@
       </c>
       <c r="I71" s="2"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <f>'DSA Problems'!A72</f>
         <v>71</v>
@@ -11098,7 +11102,7 @@
       </c>
       <c r="I72" s="2"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <f>'DSA Problems'!A73</f>
         <v>72</v>
@@ -11123,7 +11127,7 @@
       </c>
       <c r="I73" s="2"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <f>'DSA Problems'!A74</f>
         <v>73</v>
@@ -11148,7 +11152,7 @@
       </c>
       <c r="I74" s="2"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <f>'DSA Problems'!A75</f>
         <v>74</v>
@@ -11173,7 +11177,7 @@
       </c>
       <c r="I75" s="2"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <f>'DSA Problems'!A76</f>
         <v>75</v>
@@ -11198,7 +11202,7 @@
       </c>
       <c r="I76" s="2"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <f>'DSA Problems'!A77</f>
         <v>76</v>
@@ -11223,7 +11227,7 @@
       </c>
       <c r="I77" s="2"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <f>'DSA Problems'!A78</f>
         <v>77</v>
@@ -11248,7 +11252,7 @@
       </c>
       <c r="I78" s="2"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <f>'DSA Problems'!A79</f>
         <v>78</v>
@@ -11273,7 +11277,7 @@
       </c>
       <c r="I79" s="2"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <f>'DSA Problems'!A80</f>
         <v>79</v>
@@ -11298,7 +11302,7 @@
       </c>
       <c r="I80" s="2"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <f>'DSA Problems'!A81</f>
         <v>80</v>
@@ -11323,7 +11327,7 @@
       </c>
       <c r="I81" s="2"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <f>'DSA Problems'!A82</f>
         <v>81</v>
@@ -11348,7 +11352,7 @@
       </c>
       <c r="I82" s="2"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <f>'DSA Problems'!A83</f>
         <v>82</v>
@@ -11373,7 +11377,7 @@
       </c>
       <c r="I83" s="2"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <f>'DSA Problems'!A84</f>
         <v>83</v>
@@ -11398,7 +11402,7 @@
       </c>
       <c r="I84" s="2"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <f>'DSA Problems'!A85</f>
         <v>84</v>
@@ -11423,7 +11427,7 @@
       </c>
       <c r="I85" s="2"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <f>'DSA Problems'!A86</f>
         <v>85</v>
@@ -11448,7 +11452,7 @@
       </c>
       <c r="I86" s="2"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <f>'DSA Problems'!A87</f>
         <v>86</v>
@@ -11473,7 +11477,7 @@
       </c>
       <c r="I87" s="2"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <f>'DSA Problems'!A88</f>
         <v>87</v>
@@ -11498,7 +11502,7 @@
       </c>
       <c r="I88" s="2"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <f>'DSA Problems'!A89</f>
         <v>88</v>
@@ -11523,7 +11527,7 @@
       </c>
       <c r="I89" s="2"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <f>'DSA Problems'!A90</f>
         <v>89</v>
@@ -11548,7 +11552,7 @@
       </c>
       <c r="I90" s="2"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <f>'DSA Problems'!A91</f>
         <v>90</v>
@@ -11573,7 +11577,7 @@
       </c>
       <c r="I91" s="2"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <f>'DSA Problems'!A92</f>
         <v>91</v>
@@ -11598,7 +11602,7 @@
       </c>
       <c r="I92" s="2"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <f>'DSA Problems'!A93</f>
         <v>92</v>
@@ -11623,7 +11627,7 @@
       </c>
       <c r="I93" s="2"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <f>'DSA Problems'!A94</f>
         <v>93</v>
@@ -11648,7 +11652,7 @@
       </c>
       <c r="I94" s="2"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <f>'DSA Problems'!A95</f>
         <v>94</v>
@@ -11673,7 +11677,7 @@
       </c>
       <c r="I95" s="2"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <f>'DSA Problems'!A96</f>
         <v>95</v>
@@ -11698,7 +11702,7 @@
       </c>
       <c r="I96" s="2"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <f>'DSA Problems'!A97</f>
         <v>96</v>
@@ -11723,7 +11727,7 @@
       </c>
       <c r="I97" s="2"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <f>'DSA Problems'!A98</f>
         <v>97</v>
@@ -11748,7 +11752,7 @@
       </c>
       <c r="I98" s="2"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <f>'DSA Problems'!A99</f>
         <v>98</v>
@@ -11773,7 +11777,7 @@
       </c>
       <c r="I99" s="2"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <f>'DSA Problems'!A100</f>
         <v>99</v>
@@ -11798,7 +11802,7 @@
       </c>
       <c r="I100" s="2"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <f>'DSA Problems'!A101</f>
         <v>100</v>
@@ -11823,7 +11827,7 @@
       </c>
       <c r="I101" s="2"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <f>'DSA Problems'!A102</f>
         <v>101</v>
@@ -11848,7 +11852,7 @@
       </c>
       <c r="I102" s="2"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <f>'DSA Problems'!A103</f>
         <v>102</v>
@@ -11873,7 +11877,7 @@
       </c>
       <c r="I103" s="2"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <f>'DSA Problems'!A104</f>
         <v>103</v>
@@ -11898,7 +11902,7 @@
       </c>
       <c r="I104" s="2"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <f>'DSA Problems'!A105</f>
         <v>104</v>
@@ -11923,7 +11927,7 @@
       </c>
       <c r="I105" s="2"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <f>'DSA Problems'!A106</f>
         <v>105</v>
@@ -11948,7 +11952,7 @@
       </c>
       <c r="I106" s="2"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <f>'DSA Problems'!A107</f>
         <v>106</v>
@@ -11973,7 +11977,7 @@
       </c>
       <c r="I107" s="2"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <f>'DSA Problems'!A108</f>
         <v>107</v>
@@ -11998,7 +12002,7 @@
       </c>
       <c r="I108" s="2"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <f>'DSA Problems'!A109</f>
         <v>108</v>
@@ -12023,7 +12027,7 @@
       </c>
       <c r="I109" s="2"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <f>'DSA Problems'!A110</f>
         <v>109</v>
@@ -12048,7 +12052,7 @@
       </c>
       <c r="I110" s="2"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <f>'DSA Problems'!A111</f>
         <v>110</v>
@@ -12073,7 +12077,7 @@
       </c>
       <c r="I111" s="2"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <f>'DSA Problems'!A112</f>
         <v>111</v>
@@ -12098,7 +12102,7 @@
       </c>
       <c r="I112" s="2"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <f>'DSA Problems'!A113</f>
         <v>112</v>
@@ -12123,7 +12127,7 @@
       </c>
       <c r="I113" s="2"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <f>'DSA Problems'!A114</f>
         <v>113</v>
@@ -12148,7 +12152,7 @@
       </c>
       <c r="I114" s="2"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <f>'DSA Problems'!A115</f>
         <v>114</v>
@@ -12173,7 +12177,7 @@
       </c>
       <c r="I115" s="2"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <f>'DSA Problems'!A116</f>
         <v>115</v>
@@ -12198,7 +12202,7 @@
       </c>
       <c r="I116" s="2"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <f>'DSA Problems'!A117</f>
         <v>116</v>
@@ -12223,7 +12227,7 @@
       </c>
       <c r="I117" s="2"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <f>'DSA Problems'!A118</f>
         <v>117</v>
@@ -12248,7 +12252,7 @@
       </c>
       <c r="I118" s="2"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <f>'DSA Problems'!A119</f>
         <v>118</v>
@@ -12273,7 +12277,7 @@
       </c>
       <c r="I119" s="2"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <f>'DSA Problems'!A120</f>
         <v>119</v>
@@ -12298,7 +12302,7 @@
       </c>
       <c r="I120" s="2"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <f>'DSA Problems'!A121</f>
         <v>120</v>
@@ -12323,7 +12327,7 @@
       </c>
       <c r="I121" s="2"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <f>'DSA Problems'!A122</f>
         <v>121</v>
@@ -12348,7 +12352,7 @@
       </c>
       <c r="I122" s="2"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <f>'DSA Problems'!A123</f>
         <v>122</v>
@@ -12373,7 +12377,7 @@
       </c>
       <c r="I123" s="2"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <f>'DSA Problems'!A124</f>
         <v>123</v>
@@ -12398,7 +12402,7 @@
       </c>
       <c r="I124" s="2"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <f>'DSA Problems'!A125</f>
         <v>124</v>
@@ -12423,7 +12427,7 @@
       </c>
       <c r="I125" s="2"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <f>'DSA Problems'!A126</f>
         <v>125</v>
@@ -12448,7 +12452,7 @@
       </c>
       <c r="I126" s="2"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <f>'DSA Problems'!A127</f>
         <v>126</v>
@@ -12473,7 +12477,7 @@
       </c>
       <c r="I127" s="2"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <f>'DSA Problems'!A128</f>
         <v>127</v>
@@ -12498,7 +12502,7 @@
       </c>
       <c r="I128" s="2"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <f>'DSA Problems'!A129</f>
         <v>128</v>
@@ -12523,7 +12527,7 @@
       </c>
       <c r="I129" s="2"/>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <f>'DSA Problems'!A130</f>
         <v>129</v>
@@ -12548,7 +12552,7 @@
       </c>
       <c r="I130" s="2"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <f>'DSA Problems'!A131</f>
         <v>130</v>
@@ -12573,7 +12577,7 @@
       </c>
       <c r="I131" s="2"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <f>'DSA Problems'!A132</f>
         <v>131</v>
@@ -12598,7 +12602,7 @@
       </c>
       <c r="I132" s="2"/>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <f>'DSA Problems'!A133</f>
         <v>132</v>
@@ -12623,7 +12627,7 @@
       </c>
       <c r="I133" s="2"/>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <f>'DSA Problems'!A134</f>
         <v>133</v>
@@ -12648,7 +12652,7 @@
       </c>
       <c r="I134" s="2"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <f>'DSA Problems'!A135</f>
         <v>134</v>
@@ -12673,7 +12677,7 @@
       </c>
       <c r="I135" s="2"/>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <f>'DSA Problems'!A136</f>
         <v>135</v>
@@ -12698,7 +12702,7 @@
       </c>
       <c r="I136" s="2"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <f>'DSA Problems'!A137</f>
         <v>136</v>
@@ -12723,7 +12727,7 @@
       </c>
       <c r="I137" s="2"/>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <f>'DSA Problems'!A138</f>
         <v>137</v>
@@ -12748,7 +12752,7 @@
       </c>
       <c r="I138" s="2"/>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
         <f>'DSA Problems'!A139</f>
         <v>138</v>
@@ -12773,7 +12777,7 @@
       </c>
       <c r="I139" s="2"/>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <f>'DSA Problems'!A140</f>
         <v>139</v>
@@ -12798,7 +12802,7 @@
       </c>
       <c r="I140" s="2"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A141" s="2">
         <f>'DSA Problems'!A141</f>
         <v>140</v>
@@ -12823,7 +12827,7 @@
       </c>
       <c r="I141" s="2"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <f>'DSA Problems'!A142</f>
         <v>141</v>
@@ -12848,7 +12852,7 @@
       </c>
       <c r="I142" s="2"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143" s="2">
         <f>'DSA Problems'!A143</f>
         <v>142</v>
@@ -12873,7 +12877,7 @@
       </c>
       <c r="I143" s="2"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144" s="2">
         <f>'DSA Problems'!A144</f>
         <v>143</v>
@@ -12898,7 +12902,7 @@
       </c>
       <c r="I144" s="2"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145" s="2">
         <f>'DSA Problems'!A145</f>
         <v>144</v>
@@ -12923,7 +12927,7 @@
       </c>
       <c r="I145" s="2"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" s="2">
         <f>'DSA Problems'!A146</f>
         <v>145</v>
@@ -12948,7 +12952,7 @@
       </c>
       <c r="I146" s="2"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147" s="2">
         <f>'DSA Problems'!A147</f>
         <v>146</v>
@@ -12973,7 +12977,7 @@
       </c>
       <c r="I147" s="2"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148" s="2">
         <f>'DSA Problems'!A148</f>
         <v>147</v>
@@ -12998,7 +13002,7 @@
       </c>
       <c r="I148" s="2"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" s="2">
         <f>'DSA Problems'!A149</f>
         <v>148</v>
@@ -13023,7 +13027,7 @@
       </c>
       <c r="I149" s="2"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" s="2">
         <f>'DSA Problems'!A150</f>
         <v>149</v>
@@ -13048,7 +13052,7 @@
       </c>
       <c r="I150" s="2"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" s="2">
         <f>'DSA Problems'!A151</f>
         <v>150</v>
@@ -13073,7 +13077,7 @@
       </c>
       <c r="I151" s="2"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152" s="2">
         <f>'DSA Problems'!A152</f>
         <v>151</v>
@@ -13098,7 +13102,7 @@
       </c>
       <c r="I152" s="2"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153" s="2">
         <f>'DSA Problems'!A153</f>
         <v>152</v>
@@ -13123,7 +13127,7 @@
       </c>
       <c r="I153" s="2"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154" s="2">
         <f>'DSA Problems'!A154</f>
         <v>153</v>
@@ -13148,7 +13152,7 @@
       </c>
       <c r="I154" s="2"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" s="2">
         <f>'DSA Problems'!A155</f>
         <v>154</v>
@@ -13173,7 +13177,7 @@
       </c>
       <c r="I155" s="2"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" s="2">
         <f>'DSA Problems'!A156</f>
         <v>155</v>
@@ -13198,7 +13202,7 @@
       </c>
       <c r="I156" s="2"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157" s="2">
         <f>'DSA Problems'!A157</f>
         <v>156</v>
@@ -13223,7 +13227,7 @@
       </c>
       <c r="I157" s="2"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158" s="2">
         <f>'DSA Problems'!A158</f>
         <v>157</v>
@@ -13248,7 +13252,7 @@
       </c>
       <c r="I158" s="2"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159" s="2">
         <f>'DSA Problems'!A159</f>
         <v>158</v>
@@ -13273,7 +13277,7 @@
       </c>
       <c r="I159" s="2"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160" s="2">
         <f>'DSA Problems'!A160</f>
         <v>159</v>
@@ -13298,7 +13302,7 @@
       </c>
       <c r="I160" s="2"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A161" s="2">
         <f>'DSA Problems'!A161</f>
         <v>160</v>
@@ -13323,7 +13327,7 @@
       </c>
       <c r="I161" s="2"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A162" s="2">
         <f>'DSA Problems'!A162</f>
         <v>161</v>
@@ -13348,7 +13352,7 @@
       </c>
       <c r="I162" s="2"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A163" s="2">
         <f>'DSA Problems'!A163</f>
         <v>162</v>
@@ -13373,7 +13377,7 @@
       </c>
       <c r="I163" s="2"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A164" s="2">
         <f>'DSA Problems'!A164</f>
         <v>163</v>
@@ -13398,7 +13402,7 @@
       </c>
       <c r="I164" s="2"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A165" s="2">
         <f>'DSA Problems'!A165</f>
         <v>164</v>
@@ -13423,7 +13427,7 @@
       </c>
       <c r="I165" s="2"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A166" s="2">
         <f>'DSA Problems'!A166</f>
         <v>165</v>
@@ -13448,7 +13452,7 @@
       </c>
       <c r="I166" s="2"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A167" s="2">
         <f>'DSA Problems'!A167</f>
         <v>166</v>
@@ -13473,7 +13477,7 @@
       </c>
       <c r="I167" s="2"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A168" s="2">
         <f>'DSA Problems'!A168</f>
         <v>167</v>
@@ -13498,7 +13502,7 @@
       </c>
       <c r="I168" s="2"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A169" s="2">
         <f>'DSA Problems'!A169</f>
         <v>168</v>
@@ -13523,7 +13527,7 @@
       </c>
       <c r="I169" s="2"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A170" s="2">
         <f>'DSA Problems'!A170</f>
         <v>169</v>
@@ -13548,7 +13552,7 @@
       </c>
       <c r="I170" s="2"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A171" s="2">
         <f>'DSA Problems'!A171</f>
         <v>170</v>
@@ -13573,7 +13577,7 @@
       </c>
       <c r="I171" s="2"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A172" s="2">
         <f>'DSA Problems'!A172</f>
         <v>171</v>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F46F43F-AFAD-4017-8772-62300F7B79E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486F7E66-F734-4146-8B64-987D2B381DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -4867,9 +4867,11 @@
         <v>76</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G29" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G29" s="2">
+        <v>30</v>
+      </c>
       <c r="H29" s="2" t="s">
         <v>77</v>
       </c>
@@ -4895,9 +4897,11 @@
         <v>76</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G30" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G30" s="2">
+        <v>30</v>
+      </c>
       <c r="H30" s="2" t="s">
         <v>77</v>
       </c>
@@ -10017,7 +10021,7 @@
       </c>
       <c r="D29" s="2" t="str">
         <f>'DSA Problems'!F29</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
@@ -10042,7 +10046,7 @@
       </c>
       <c r="D30" s="2" t="str">
         <f>'DSA Problems'!F30</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486F7E66-F734-4146-8B64-987D2B381DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{535BAFBF-784A-43A0-977A-9B899E56499A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -4927,9 +4927,11 @@
         <v>76</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G31" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G31" s="2">
+        <v>40</v>
+      </c>
       <c r="H31" s="2" t="s">
         <v>77</v>
       </c>
@@ -10071,7 +10073,7 @@
       </c>
       <c r="D31" s="2" t="str">
         <f>'DSA Problems'!F31</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{535BAFBF-784A-43A0-977A-9B899E56499A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FDA038-68A8-43FE-866E-6BE04D32275C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B6" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"In Progress")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -4957,9 +4957,11 @@
         <v>76</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G32" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G32" s="2">
+        <v>40</v>
+      </c>
       <c r="H32" s="2" t="s">
         <v>77</v>
       </c>
@@ -4985,7 +4987,7 @@
         <v>76</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2" t="s">
@@ -10098,7 +10100,7 @@
       </c>
       <c r="D32" s="2" t="str">
         <f>'DSA Problems'!F32</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -10123,7 +10125,7 @@
       </c>
       <c r="D33" s="2" t="str">
         <f>'DSA Problems'!F33</f>
-        <v>Not Started</v>
+        <v>In Progress</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FDA038-68A8-43FE-866E-6BE04D32275C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350E8E1C-918D-4577-AC8E-7378D5371051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -4987,9 +4987,11 @@
         <v>76</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G33" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G33" s="2">
+        <v>40</v>
+      </c>
       <c r="H33" s="2" t="s">
         <v>77</v>
       </c>
@@ -5015,9 +5017,11 @@
         <v>76</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G34" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G34" s="2">
+        <v>40</v>
+      </c>
       <c r="H34" s="2" t="s">
         <v>77</v>
       </c>
@@ -5043,7 +5047,7 @@
         <v>76</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2" t="s">
@@ -10125,7 +10129,7 @@
       </c>
       <c r="D33" s="2" t="str">
         <f>'DSA Problems'!F33</f>
-        <v>In Progress</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -10150,7 +10154,7 @@
       </c>
       <c r="D34" s="2" t="str">
         <f>'DSA Problems'!F34</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
@@ -10175,7 +10179,7 @@
       </c>
       <c r="D35" s="2" t="str">
         <f>'DSA Problems'!F35</f>
-        <v>Not Started</v>
+        <v>In Progress</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350E8E1C-918D-4577-AC8E-7378D5371051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{209BE3FA-7978-4802-9796-D024DE127AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B6" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"In Progress")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -5047,9 +5047,11 @@
         <v>76</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G35" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G35" s="2">
+        <v>40</v>
+      </c>
       <c r="H35" s="2" t="s">
         <v>77</v>
       </c>
@@ -10179,7 +10181,7 @@
       </c>
       <c r="D35" s="2" t="str">
         <f>'DSA Problems'!F35</f>
-        <v>In Progress</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{209BE3FA-7978-4802-9796-D024DE127AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E95F12C-E015-40B7-98C2-05ED20D1944F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -5077,9 +5077,11 @@
         <v>76</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G36" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G36" s="2">
+        <v>45</v>
+      </c>
       <c r="H36" s="2" t="s">
         <v>77</v>
       </c>
@@ -10206,7 +10208,7 @@
       </c>
       <c r="D36" s="2" t="str">
         <f>'DSA Problems'!F36</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E95F12C-E015-40B7-98C2-05ED20D1944F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE40B900-4B2F-44BF-990E-EC7F27956094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="14400" windowHeight="8170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -5107,9 +5107,11 @@
         <v>76</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G37" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G37" s="2">
+        <v>25</v>
+      </c>
       <c r="H37" s="2" t="s">
         <v>77</v>
       </c>
@@ -5135,9 +5137,11 @@
         <v>76</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G38" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G38" s="2">
+        <v>25</v>
+      </c>
       <c r="H38" s="2" t="s">
         <v>77</v>
       </c>
@@ -5191,9 +5195,11 @@
         <v>76</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G40" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G40" s="2">
+        <v>25</v>
+      </c>
       <c r="H40" s="2" t="s">
         <v>77</v>
       </c>
@@ -10233,7 +10239,7 @@
       </c>
       <c r="D37" s="2" t="str">
         <f>'DSA Problems'!F37</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
@@ -10258,7 +10264,7 @@
       </c>
       <c r="D38" s="2" t="str">
         <f>'DSA Problems'!F38</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
@@ -10308,7 +10314,7 @@
       </c>
       <c r="D40" s="2" t="str">
         <f>'DSA Problems'!F40</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE40B900-4B2F-44BF-990E-EC7F27956094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{691AA9C9-7C66-4B5A-86C2-B25DEB5D8791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="14400" windowHeight="8170" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -5225,9 +5225,11 @@
         <v>118</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G41" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G41" s="2">
+        <v>20</v>
+      </c>
       <c r="H41" s="2" t="s">
         <v>77</v>
       </c>
@@ -10339,7 +10341,7 @@
       </c>
       <c r="D41" s="2" t="str">
         <f>'DSA Problems'!F41</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{691AA9C9-7C66-4B5A-86C2-B25DEB5D8791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08EB1B43-E643-46E7-9A31-E0807B2B8FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1830" uniqueCount="253">
   <si>
     <t>DSA 90-Day Interview Preparation Dashboard</t>
   </si>
@@ -795,6 +795,9 @@
   </si>
   <si>
     <t>it cannot be executed local</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> I have to relearn it</t>
   </si>
 </sst>
 </file>
@@ -1220,7 +1223,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -5167,9 +5170,11 @@
         <v>76</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G39" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G39" s="2">
+        <v>25</v>
+      </c>
       <c r="H39" s="2" t="s">
         <v>77</v>
       </c>
@@ -5264,7 +5269,9 @@
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
-      <c r="L42" s="2"/>
+      <c r="L42" s="2" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
@@ -5283,9 +5290,11 @@
         <v>118</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G43" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G43" s="2">
+        <v>25</v>
+      </c>
       <c r="H43" s="2" t="s">
         <v>77</v>
       </c>
@@ -5311,9 +5320,11 @@
         <v>118</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G44" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G44" s="2">
+        <v>25</v>
+      </c>
       <c r="H44" s="2" t="s">
         <v>77</v>
       </c>
@@ -5339,9 +5350,11 @@
         <v>118</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G45" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G45" s="2">
+        <v>25</v>
+      </c>
       <c r="H45" s="2" t="s">
         <v>77</v>
       </c>
@@ -5367,9 +5380,11 @@
         <v>118</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G46" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G46" s="2">
+        <v>25</v>
+      </c>
       <c r="H46" s="2" t="s">
         <v>77</v>
       </c>
@@ -10291,7 +10306,7 @@
       </c>
       <c r="D39" s="2" t="str">
         <f>'DSA Problems'!F39</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
@@ -10391,7 +10406,7 @@
       </c>
       <c r="D43" s="2" t="str">
         <f>'DSA Problems'!F43</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
@@ -10416,7 +10431,7 @@
       </c>
       <c r="D44" s="2" t="str">
         <f>'DSA Problems'!F44</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
@@ -10441,7 +10456,7 @@
       </c>
       <c r="D45" s="2" t="str">
         <f>'DSA Problems'!F45</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
@@ -10466,7 +10481,7 @@
       </c>
       <c r="D46" s="2" t="str">
         <f>'DSA Problems'!F46</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08EB1B43-E643-46E7-9A31-E0807B2B8FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B865D4-0A08-497B-BBE1-6751FB20B068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B865D4-0A08-497B-BBE1-6751FB20B068}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EBA2AE1-9003-4D48-9447-CD962ED2EB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -5556,9 +5556,11 @@
         <v>76</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G52" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G52" s="2">
+        <v>20</v>
+      </c>
       <c r="H52" s="2" t="s">
         <v>77</v>
       </c>
@@ -5584,9 +5586,11 @@
         <v>76</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G53" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G53" s="2">
+        <v>20</v>
+      </c>
       <c r="H53" s="2" t="s">
         <v>77</v>
       </c>
@@ -5612,9 +5616,11 @@
         <v>76</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G54" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G54" s="2">
+        <v>20</v>
+      </c>
       <c r="H54" s="2" t="s">
         <v>77</v>
       </c>
@@ -10631,7 +10637,7 @@
       </c>
       <c r="D52" s="2" t="str">
         <f>'DSA Problems'!F52</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
@@ -10656,7 +10662,7 @@
       </c>
       <c r="D53" s="2" t="str">
         <f>'DSA Problems'!F53</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
@@ -10681,7 +10687,7 @@
       </c>
       <c r="D54" s="2" t="str">
         <f>'DSA Problems'!F54</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EBA2AE1-9003-4D48-9447-CD962ED2EB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9076C9D-C0D1-4E1C-8F3B-579A55A77725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -5646,9 +5646,11 @@
         <v>76</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G55" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G55" s="2">
+        <v>20</v>
+      </c>
       <c r="H55" s="2" t="s">
         <v>77</v>
       </c>
@@ -5674,9 +5676,11 @@
         <v>76</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G56" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G56" s="2">
+        <v>20</v>
+      </c>
       <c r="H56" s="2" t="s">
         <v>77</v>
       </c>
@@ -10712,7 +10716,7 @@
       </c>
       <c r="D55" s="2" t="str">
         <f>'DSA Problems'!F55</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
@@ -10737,7 +10741,7 @@
       </c>
       <c r="D56" s="2" t="str">
         <f>'DSA Problems'!F56</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9076C9D-C0D1-4E1C-8F3B-579A55A77725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBF943B-C718-48D9-92DE-BC31B34ED18A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -5706,9 +5706,11 @@
         <v>76</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G57" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G57" s="2">
+        <v>25</v>
+      </c>
       <c r="H57" s="2" t="s">
         <v>77</v>
       </c>
@@ -5734,9 +5736,11 @@
         <v>76</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G58" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G58" s="2">
+        <v>20</v>
+      </c>
       <c r="H58" s="2" t="s">
         <v>77</v>
       </c>
@@ -10766,7 +10770,7 @@
       </c>
       <c r="D57" s="2" t="str">
         <f>'DSA Problems'!F57</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
@@ -10791,7 +10795,7 @@
       </c>
       <c r="D58" s="2" t="str">
         <f>'DSA Problems'!F58</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>

--- a/documents/plan/DSA_90_Day_Roadmap.xlsx
+++ b/documents/plan/DSA_90_Day_Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SreenivasReddyDaram\Target-learn\documents\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBF943B-C718-48D9-92DE-BC31B34ED18A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE8BA70-0696-4430-B27B-B176A82E8B2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B7" s="2">
         <f>COUNTIF('DSA Problems'!F:F,"Needs Revision")</f>
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -5822,9 +5822,11 @@
         <v>76</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G61" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G61" s="2">
+        <v>20</v>
+      </c>
       <c r="H61" s="2" t="s">
         <v>77</v>
       </c>
@@ -5850,9 +5852,11 @@
         <v>76</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G62" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="G62" s="2">
+        <v>15</v>
+      </c>
       <c r="H62" s="2" t="s">
         <v>77</v>
       </c>
@@ -10870,7 +10874,7 @@
       </c>
       <c r="D61" s="2" t="str">
         <f>'DSA Problems'!F61</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
@@ -10895,7 +10899,7 @@
       </c>
       <c r="D62" s="2" t="str">
         <f>'DSA Problems'!F62</f>
-        <v>Not Started</v>
+        <v>Needs Revision</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" s="2"/>
